--- a/artfynd/A 57317-2024 artfynd.xlsx
+++ b/artfynd/A 57317-2024 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122384843</v>
+        <v>122384291</v>
       </c>
       <c r="B3" t="n">
-        <v>57390</v>
+        <v>90797</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,27 +803,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -832,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563208</v>
+        <v>563130</v>
       </c>
       <c r="R3" t="n">
-        <v>7040782</v>
+        <v>7040874</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,22 +896,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122384291</v>
+        <v>122384843</v>
       </c>
       <c r="B4" t="n">
-        <v>90797</v>
+        <v>57390</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,31 +924,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -953,10 +953,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563130</v>
+        <v>563208</v>
       </c>
       <c r="R4" t="n">
-        <v>7040874</v>
+        <v>7040782</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -988,7 +988,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,12 +1013,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1147,10 +1147,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122382572</v>
+        <v>122381532</v>
       </c>
       <c r="B6" t="n">
-        <v>98175</v>
+        <v>78645</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1159,42 +1159,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563035</v>
+        <v>563324</v>
       </c>
       <c r="R6" t="n">
-        <v>7040943</v>
+        <v>7040908</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1226,7 +1222,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1236,7 +1232,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1263,10 +1259,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122381532</v>
+        <v>122382572</v>
       </c>
       <c r="B7" t="n">
-        <v>78645</v>
+        <v>98175</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1275,38 +1271,42 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>563324</v>
+        <v>563035</v>
       </c>
       <c r="R7" t="n">
-        <v>7040908</v>
+        <v>7040943</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1338,7 +1338,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1609,10 +1609,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122382726</v>
+        <v>122381949</v>
       </c>
       <c r="B10" t="n">
-        <v>90797</v>
+        <v>79726</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1625,21 +1625,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1649,10 +1649,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>563044</v>
+        <v>563164</v>
       </c>
       <c r="R10" t="n">
-        <v>7040945</v>
+        <v>7040871</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1721,10 +1721,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122382979</v>
+        <v>122382726</v>
       </c>
       <c r="B11" t="n">
-        <v>57374</v>
+        <v>90797</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1737,39 +1737,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>562944</v>
+        <v>563044</v>
       </c>
       <c r="R11" t="n">
-        <v>7041093</v>
+        <v>7040945</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1801,7 +1796,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1811,12 +1806,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:45</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1843,10 +1833,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122381949</v>
+        <v>122382979</v>
       </c>
       <c r="B12" t="n">
-        <v>79726</v>
+        <v>57374</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1859,34 +1849,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>563164</v>
+        <v>562944</v>
       </c>
       <c r="R12" t="n">
-        <v>7040871</v>
+        <v>7041093</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1918,7 +1913,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1928,7 +1923,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2739,10 +2739,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122383248</v>
+        <v>122384433</v>
       </c>
       <c r="B20" t="n">
-        <v>90797</v>
+        <v>57374</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2755,34 +2755,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>562917</v>
+        <v>563163</v>
       </c>
       <c r="R20" t="n">
-        <v>7041224</v>
+        <v>7040839</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2814,7 +2819,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2824,7 +2829,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2839,22 +2849,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122384433</v>
+        <v>122383248</v>
       </c>
       <c r="B21" t="n">
-        <v>57374</v>
+        <v>90797</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2867,39 +2877,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>563163</v>
+        <v>562917</v>
       </c>
       <c r="R21" t="n">
-        <v>7040839</v>
+        <v>7041224</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2931,7 +2936,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2941,12 +2946,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:52</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2961,12 +2961,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>

--- a/artfynd/A 57317-2024 artfynd.xlsx
+++ b/artfynd/A 57317-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122382824</v>
+        <v>122382243</v>
       </c>
       <c r="B2" t="n">
-        <v>78645</v>
+        <v>78646</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>563010</v>
+        <v>563125</v>
       </c>
       <c r="R2" t="n">
-        <v>7041054</v>
+        <v>7040906</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,22 +775,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122384291</v>
+        <v>122384637</v>
       </c>
       <c r="B3" t="n">
-        <v>90797</v>
+        <v>90807</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -820,26 +820,17 @@
           <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563130</v>
+        <v>563210</v>
       </c>
       <c r="R3" t="n">
-        <v>7040874</v>
+        <v>7040790</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,22 +887,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122384843</v>
+        <v>122381544</v>
       </c>
       <c r="B4" t="n">
-        <v>57390</v>
+        <v>78646</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -924,39 +915,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563208</v>
+        <v>563309</v>
       </c>
       <c r="R4" t="n">
-        <v>7040782</v>
+        <v>7040893</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -988,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -998,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122384829</v>
+        <v>122381802</v>
       </c>
       <c r="B5" t="n">
-        <v>57374</v>
+        <v>90807</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1041,39 +1027,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563205</v>
+        <v>563191</v>
       </c>
       <c r="R5" t="n">
-        <v>7040789</v>
+        <v>7040857</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1105,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1115,12 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:16</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1147,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122381532</v>
+        <v>122382979</v>
       </c>
       <c r="B6" t="n">
-        <v>78645</v>
+        <v>57374</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1163,34 +1139,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563324</v>
+        <v>562944</v>
       </c>
       <c r="R6" t="n">
-        <v>7040908</v>
+        <v>7041093</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1222,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1232,7 +1213,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1259,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122382572</v>
+        <v>122384843</v>
       </c>
       <c r="B7" t="n">
-        <v>98175</v>
+        <v>57390</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1271,30 +1257,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1303,10 +1290,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>563035</v>
+        <v>563208</v>
       </c>
       <c r="R7" t="n">
-        <v>7040943</v>
+        <v>7040782</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1338,7 +1325,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1348,7 +1335,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1375,10 +1362,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122382457</v>
+        <v>122383327</v>
       </c>
       <c r="B8" t="n">
-        <v>90779</v>
+        <v>90807</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1391,21 +1378,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1415,10 +1402,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>563028</v>
+        <v>562914</v>
       </c>
       <c r="R8" t="n">
-        <v>7040950</v>
+        <v>7041282</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1450,7 +1437,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1460,7 +1447,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1487,10 +1474,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122383513</v>
+        <v>122381949</v>
       </c>
       <c r="B9" t="n">
-        <v>57374</v>
+        <v>79727</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1503,39 +1490,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>562901</v>
+        <v>563164</v>
       </c>
       <c r="R9" t="n">
-        <v>7041298</v>
+        <v>7040871</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1567,7 +1549,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1577,12 +1559,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:18</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1609,10 +1586,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122381949</v>
+        <v>122383212</v>
       </c>
       <c r="B10" t="n">
-        <v>79726</v>
+        <v>90807</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1625,21 +1602,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1649,10 +1626,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>563164</v>
+        <v>562931</v>
       </c>
       <c r="R10" t="n">
-        <v>7040871</v>
+        <v>7041192</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1684,7 +1661,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1694,7 +1671,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1721,10 +1698,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122382726</v>
+        <v>122382572</v>
       </c>
       <c r="B11" t="n">
-        <v>90797</v>
+        <v>98185</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1733,38 +1710,42 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>563044</v>
+        <v>563035</v>
       </c>
       <c r="R11" t="n">
-        <v>7040945</v>
+        <v>7040943</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1796,7 +1777,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1806,7 +1787,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1833,10 +1814,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122382979</v>
+        <v>122381980</v>
       </c>
       <c r="B12" t="n">
-        <v>57374</v>
+        <v>78646</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1849,39 +1830,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>562944</v>
+        <v>563161</v>
       </c>
       <c r="R12" t="n">
-        <v>7041093</v>
+        <v>7040863</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1913,7 +1889,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1923,12 +1899,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:45</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1955,10 +1926,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122382243</v>
+        <v>122381532</v>
       </c>
       <c r="B13" t="n">
-        <v>78645</v>
+        <v>78646</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1995,10 +1966,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>563125</v>
+        <v>563324</v>
       </c>
       <c r="R13" t="n">
-        <v>7040906</v>
+        <v>7040908</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2030,7 +2001,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2040,7 +2011,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2067,10 +2038,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122381980</v>
+        <v>122383691</v>
       </c>
       <c r="B14" t="n">
-        <v>78645</v>
+        <v>57390</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2083,34 +2054,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>563161</v>
+        <v>562911</v>
       </c>
       <c r="R14" t="n">
-        <v>7040863</v>
+        <v>7041237</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2142,7 +2118,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2152,7 +2128,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2182,7 +2158,7 @@
         <v>122381566</v>
       </c>
       <c r="B15" t="n">
-        <v>82432</v>
+        <v>82433</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2291,10 +2267,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122383212</v>
+        <v>122384433</v>
       </c>
       <c r="B16" t="n">
-        <v>90797</v>
+        <v>57374</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2307,34 +2283,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>562931</v>
+        <v>563163</v>
       </c>
       <c r="R16" t="n">
-        <v>7041192</v>
+        <v>7040839</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2366,7 +2347,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2376,7 +2357,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2391,22 +2377,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122383327</v>
+        <v>122382726</v>
       </c>
       <c r="B17" t="n">
-        <v>90797</v>
+        <v>90807</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2443,10 +2429,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>562914</v>
+        <v>563044</v>
       </c>
       <c r="R17" t="n">
-        <v>7041282</v>
+        <v>7040945</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2478,7 +2464,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2488,7 +2474,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2515,10 +2501,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122384637</v>
+        <v>122383248</v>
       </c>
       <c r="B18" t="n">
-        <v>90797</v>
+        <v>90807</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2555,10 +2541,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>563210</v>
+        <v>562917</v>
       </c>
       <c r="R18" t="n">
-        <v>7040790</v>
+        <v>7041224</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2590,7 +2576,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2600,7 +2586,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2627,10 +2613,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122381802</v>
+        <v>122384829</v>
       </c>
       <c r="B19" t="n">
-        <v>90797</v>
+        <v>57374</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2643,34 +2629,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>563191</v>
+        <v>563205</v>
       </c>
       <c r="R19" t="n">
-        <v>7040857</v>
+        <v>7040789</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2702,7 +2693,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2712,7 +2703,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2739,10 +2735,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122384433</v>
+        <v>122382457</v>
       </c>
       <c r="B20" t="n">
-        <v>57374</v>
+        <v>90789</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2755,39 +2751,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>563163</v>
+        <v>563028</v>
       </c>
       <c r="R20" t="n">
-        <v>7040839</v>
+        <v>7040950</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2819,7 +2810,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2829,12 +2820,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:52</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2849,22 +2835,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122383248</v>
+        <v>122382824</v>
       </c>
       <c r="B21" t="n">
-        <v>90797</v>
+        <v>78646</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2877,21 +2863,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2901,10 +2887,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>562917</v>
+        <v>563010</v>
       </c>
       <c r="R21" t="n">
-        <v>7041224</v>
+        <v>7041054</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2936,7 +2922,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2946,7 +2932,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2961,22 +2947,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122383691</v>
+        <v>122383513</v>
       </c>
       <c r="B22" t="n">
-        <v>57390</v>
+        <v>57374</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2989,16 +2975,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3009,7 +2995,7 @@
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3018,10 +3004,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>562911</v>
+        <v>562901</v>
       </c>
       <c r="R22" t="n">
-        <v>7041237</v>
+        <v>7041298</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3053,7 +3039,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3063,7 +3049,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3090,10 +3081,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122381544</v>
+        <v>122384291</v>
       </c>
       <c r="B23" t="n">
-        <v>78645</v>
+        <v>90807</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3106,34 +3097,43 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>563309</v>
+        <v>563130</v>
       </c>
       <c r="R23" t="n">
-        <v>7040893</v>
+        <v>7040874</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3165,7 +3165,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3190,12 +3190,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>

--- a/artfynd/A 57317-2024 artfynd.xlsx
+++ b/artfynd/A 57317-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122382243</v>
+        <v>122384433</v>
       </c>
       <c r="B2" t="n">
-        <v>78646</v>
+        <v>57374</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>563125</v>
+        <v>563163</v>
       </c>
       <c r="R2" t="n">
-        <v>7040906</v>
+        <v>7040839</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,12 +785,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -899,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122381544</v>
+        <v>122382572</v>
       </c>
       <c r="B4" t="n">
-        <v>78646</v>
+        <v>98185</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,38 +921,42 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563309</v>
+        <v>563035</v>
       </c>
       <c r="R4" t="n">
-        <v>7040893</v>
+        <v>7040943</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +988,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +998,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1025,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122381802</v>
+        <v>122381980</v>
       </c>
       <c r="B5" t="n">
-        <v>90807</v>
+        <v>78646</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,21 +1041,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1065,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563191</v>
+        <v>563161</v>
       </c>
       <c r="R5" t="n">
-        <v>7040857</v>
+        <v>7040863</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1100,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1110,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1137,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122382979</v>
+        <v>122382457</v>
       </c>
       <c r="B6" t="n">
-        <v>57374</v>
+        <v>90789</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,39 +1153,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>562944</v>
+        <v>563028</v>
       </c>
       <c r="R6" t="n">
-        <v>7041093</v>
+        <v>7040950</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1203,7 +1212,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,12 +1222,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:45</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,10 +1249,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122384843</v>
+        <v>122383248</v>
       </c>
       <c r="B7" t="n">
-        <v>57390</v>
+        <v>90807</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1261,39 +1265,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>563208</v>
+        <v>562917</v>
       </c>
       <c r="R7" t="n">
-        <v>7040782</v>
+        <v>7041224</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1325,7 +1324,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1335,7 +1334,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1362,10 +1361,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122383327</v>
+        <v>122383691</v>
       </c>
       <c r="B8" t="n">
-        <v>90807</v>
+        <v>57390</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1378,34 +1377,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>562914</v>
+        <v>562911</v>
       </c>
       <c r="R8" t="n">
-        <v>7041282</v>
+        <v>7041237</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1437,7 +1441,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1447,7 +1451,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1474,10 +1478,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122381949</v>
+        <v>122384843</v>
       </c>
       <c r="B9" t="n">
-        <v>79727</v>
+        <v>57390</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1490,34 +1494,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>563164</v>
+        <v>563208</v>
       </c>
       <c r="R9" t="n">
-        <v>7040871</v>
+        <v>7040782</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1549,7 +1558,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1559,7 +1568,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1586,7 +1595,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122383212</v>
+        <v>122384291</v>
       </c>
       <c r="B10" t="n">
         <v>90807</v>
@@ -1619,17 +1628,26 @@
           <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>562931</v>
+        <v>563130</v>
       </c>
       <c r="R10" t="n">
-        <v>7041192</v>
+        <v>7040874</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1661,7 +1679,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1671,7 +1689,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1686,22 +1704,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122382572</v>
+        <v>122381532</v>
       </c>
       <c r="B11" t="n">
-        <v>98185</v>
+        <v>78646</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1710,42 +1728,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>563035</v>
+        <v>563324</v>
       </c>
       <c r="R11" t="n">
-        <v>7040943</v>
+        <v>7040908</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1777,7 +1791,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1787,7 +1801,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1814,10 +1828,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122381980</v>
+        <v>122382726</v>
       </c>
       <c r="B12" t="n">
-        <v>78646</v>
+        <v>90807</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1830,21 +1844,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1854,10 +1868,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>563161</v>
+        <v>563044</v>
       </c>
       <c r="R12" t="n">
-        <v>7040863</v>
+        <v>7040945</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1889,7 +1903,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1899,7 +1913,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1926,10 +1940,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122381532</v>
+        <v>122383327</v>
       </c>
       <c r="B13" t="n">
-        <v>78646</v>
+        <v>90807</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1942,21 +1956,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1966,10 +1980,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>563324</v>
+        <v>562914</v>
       </c>
       <c r="R13" t="n">
-        <v>7040908</v>
+        <v>7041282</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2001,7 +2015,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2011,7 +2025,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2038,10 +2052,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122383691</v>
+        <v>122383513</v>
       </c>
       <c r="B14" t="n">
-        <v>57390</v>
+        <v>57374</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2054,16 +2068,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2074,7 +2088,7 @@
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2083,10 +2097,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>562911</v>
+        <v>562901</v>
       </c>
       <c r="R14" t="n">
-        <v>7041237</v>
+        <v>7041298</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2118,7 +2132,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2128,7 +2142,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2155,10 +2174,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122381566</v>
+        <v>122382824</v>
       </c>
       <c r="B15" t="n">
-        <v>82433</v>
+        <v>78646</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2171,21 +2190,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2195,10 +2214,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>563319</v>
+        <v>563010</v>
       </c>
       <c r="R15" t="n">
-        <v>7040899</v>
+        <v>7041054</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2230,7 +2249,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2240,7 +2259,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2255,22 +2274,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122384433</v>
+        <v>122381949</v>
       </c>
       <c r="B16" t="n">
-        <v>57374</v>
+        <v>79727</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2283,39 +2302,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>563163</v>
+        <v>563164</v>
       </c>
       <c r="R16" t="n">
-        <v>7040839</v>
+        <v>7040871</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2347,7 +2361,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2357,12 +2371,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:52</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2377,19 +2386,19 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122382726</v>
+        <v>122381802</v>
       </c>
       <c r="B17" t="n">
         <v>90807</v>
@@ -2429,10 +2438,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>563044</v>
+        <v>563191</v>
       </c>
       <c r="R17" t="n">
-        <v>7040945</v>
+        <v>7040857</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2464,7 +2473,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2474,7 +2483,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2501,7 +2510,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122383248</v>
+        <v>122383212</v>
       </c>
       <c r="B18" t="n">
         <v>90807</v>
@@ -2541,10 +2550,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>562917</v>
+        <v>562931</v>
       </c>
       <c r="R18" t="n">
-        <v>7041224</v>
+        <v>7041192</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2576,7 +2585,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2586,7 +2595,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2613,10 +2622,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122384829</v>
+        <v>122382243</v>
       </c>
       <c r="B19" t="n">
-        <v>57374</v>
+        <v>78646</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2629,39 +2638,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>563205</v>
+        <v>563125</v>
       </c>
       <c r="R19" t="n">
-        <v>7040789</v>
+        <v>7040906</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2693,7 +2697,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2703,12 +2707,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:16</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2735,10 +2734,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122382457</v>
+        <v>122382979</v>
       </c>
       <c r="B20" t="n">
-        <v>90789</v>
+        <v>57374</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2751,34 +2750,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>563028</v>
+        <v>562944</v>
       </c>
       <c r="R20" t="n">
-        <v>7040950</v>
+        <v>7041093</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2810,7 +2814,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2820,7 +2824,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2847,10 +2856,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122382824</v>
+        <v>122381566</v>
       </c>
       <c r="B21" t="n">
-        <v>78646</v>
+        <v>82433</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2863,21 +2872,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2887,10 +2896,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>563010</v>
+        <v>563319</v>
       </c>
       <c r="R21" t="n">
-        <v>7041054</v>
+        <v>7040899</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2922,7 +2931,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2932,7 +2941,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2947,19 +2956,19 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122383513</v>
+        <v>122384829</v>
       </c>
       <c r="B22" t="n">
         <v>57374</v>
@@ -2995,7 +3004,7 @@
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3004,10 +3013,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>562901</v>
+        <v>563205</v>
       </c>
       <c r="R22" t="n">
-        <v>7041298</v>
+        <v>7040789</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3039,7 +3048,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3049,7 +3058,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3081,10 +3090,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122384291</v>
+        <v>122381544</v>
       </c>
       <c r="B23" t="n">
-        <v>90807</v>
+        <v>78646</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3097,43 +3106,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>563130</v>
+        <v>563309</v>
       </c>
       <c r="R23" t="n">
-        <v>7040874</v>
+        <v>7040893</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3165,7 +3165,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3190,12 +3190,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>

--- a/artfynd/A 57317-2024 artfynd.xlsx
+++ b/artfynd/A 57317-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122384433</v>
+        <v>122384637</v>
       </c>
       <c r="B2" t="n">
-        <v>57374</v>
+        <v>90807</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>563163</v>
+        <v>563210</v>
       </c>
       <c r="R2" t="n">
-        <v>7040839</v>
+        <v>7040790</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:52</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,22 +775,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122384637</v>
+        <v>122384433</v>
       </c>
       <c r="B3" t="n">
-        <v>90807</v>
+        <v>57374</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,34 +803,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563210</v>
+        <v>563163</v>
       </c>
       <c r="R3" t="n">
-        <v>7040790</v>
+        <v>7040839</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +877,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,12 +897,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1478,10 +1478,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122384843</v>
+        <v>122384291</v>
       </c>
       <c r="B9" t="n">
-        <v>57390</v>
+        <v>90807</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1494,27 +1494,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1523,10 +1527,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>563208</v>
+        <v>563130</v>
       </c>
       <c r="R9" t="n">
-        <v>7040782</v>
+        <v>7040874</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1558,7 +1562,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1568,7 +1572,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1583,22 +1587,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122384291</v>
+        <v>122384843</v>
       </c>
       <c r="B10" t="n">
-        <v>90807</v>
+        <v>57390</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1611,31 +1615,27 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1644,10 +1644,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>563130</v>
+        <v>563208</v>
       </c>
       <c r="R10" t="n">
-        <v>7040874</v>
+        <v>7040782</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1689,7 +1689,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1704,12 +1704,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>

--- a/artfynd/A 57317-2024 artfynd.xlsx
+++ b/artfynd/A 57317-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122384637</v>
       </c>
       <c r="B2" t="n">
-        <v>90807</v>
+        <v>90819</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122384433</v>
+        <v>122383691</v>
       </c>
       <c r="B3" t="n">
-        <v>57374</v>
+        <v>57395</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,16 +803,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563163</v>
+        <v>562911</v>
       </c>
       <c r="R3" t="n">
-        <v>7040839</v>
+        <v>7041237</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:52</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,22 +892,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122382572</v>
+        <v>122384291</v>
       </c>
       <c r="B4" t="n">
-        <v>98185</v>
+        <v>90819</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,25 +916,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -947,16 +942,21 @@
           <t>3</t>
         </is>
       </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563035</v>
+        <v>563130</v>
       </c>
       <c r="R4" t="n">
-        <v>7040943</v>
+        <v>7040874</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -988,7 +988,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,12 +1013,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1028,7 +1028,7 @@
         <v>122381980</v>
       </c>
       <c r="B5" t="n">
-        <v>78646</v>
+        <v>78651</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1137,10 +1137,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122382457</v>
+        <v>122381566</v>
       </c>
       <c r="B6" t="n">
-        <v>90789</v>
+        <v>82438</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1153,21 +1153,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1177,10 +1177,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563028</v>
+        <v>563319</v>
       </c>
       <c r="R6" t="n">
-        <v>7040950</v>
+        <v>7040899</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1249,10 +1249,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122383248</v>
+        <v>122382457</v>
       </c>
       <c r="B7" t="n">
-        <v>90807</v>
+        <v>90801</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1265,21 +1265,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1289,10 +1289,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>562917</v>
+        <v>563028</v>
       </c>
       <c r="R7" t="n">
-        <v>7041224</v>
+        <v>7040950</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1361,10 +1361,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122383691</v>
+        <v>122381802</v>
       </c>
       <c r="B8" t="n">
-        <v>57390</v>
+        <v>90819</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1377,39 +1377,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>562911</v>
+        <v>563191</v>
       </c>
       <c r="R8" t="n">
-        <v>7041237</v>
+        <v>7040857</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1441,7 +1436,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1451,7 +1446,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1478,10 +1473,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122384291</v>
+        <v>122384843</v>
       </c>
       <c r="B9" t="n">
-        <v>90807</v>
+        <v>57395</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1494,31 +1489,27 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1527,10 +1518,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>563130</v>
+        <v>563208</v>
       </c>
       <c r="R9" t="n">
-        <v>7040874</v>
+        <v>7040782</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1562,7 +1553,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1572,7 +1563,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1587,22 +1578,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122384843</v>
+        <v>122383327</v>
       </c>
       <c r="B10" t="n">
-        <v>57390</v>
+        <v>90819</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1615,39 +1606,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>563208</v>
+        <v>562914</v>
       </c>
       <c r="R10" t="n">
-        <v>7040782</v>
+        <v>7041282</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1679,7 +1665,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1689,7 +1675,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1716,10 +1702,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122381532</v>
+        <v>122384829</v>
       </c>
       <c r="B11" t="n">
-        <v>78646</v>
+        <v>57379</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1732,34 +1718,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>563324</v>
+        <v>563205</v>
       </c>
       <c r="R11" t="n">
-        <v>7040908</v>
+        <v>7040789</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1791,7 +1782,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1801,7 +1792,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1828,10 +1824,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122382726</v>
+        <v>122382979</v>
       </c>
       <c r="B12" t="n">
-        <v>90807</v>
+        <v>57379</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1844,34 +1840,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>563044</v>
+        <v>562944</v>
       </c>
       <c r="R12" t="n">
-        <v>7040945</v>
+        <v>7041093</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1903,7 +1904,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1913,7 +1914,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1940,10 +1946,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122383327</v>
+        <v>122383248</v>
       </c>
       <c r="B13" t="n">
-        <v>90807</v>
+        <v>90819</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1980,10 +1986,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>562914</v>
+        <v>562917</v>
       </c>
       <c r="R13" t="n">
-        <v>7041282</v>
+        <v>7041224</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2015,7 +2021,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2025,7 +2031,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2052,10 +2058,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122383513</v>
+        <v>122384433</v>
       </c>
       <c r="B14" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2088,7 +2094,7 @@
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2097,10 +2103,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>562901</v>
+        <v>563163</v>
       </c>
       <c r="R14" t="n">
-        <v>7041298</v>
+        <v>7040839</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2132,7 +2138,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2142,12 +2148,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2162,12 +2168,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2177,7 +2183,7 @@
         <v>122382824</v>
       </c>
       <c r="B15" t="n">
-        <v>78646</v>
+        <v>78651</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2286,10 +2292,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122381949</v>
+        <v>122382243</v>
       </c>
       <c r="B16" t="n">
-        <v>79727</v>
+        <v>78651</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2302,21 +2308,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2326,10 +2332,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>563164</v>
+        <v>563125</v>
       </c>
       <c r="R16" t="n">
-        <v>7040871</v>
+        <v>7040906</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2361,7 +2367,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2371,7 +2377,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2398,10 +2404,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122381802</v>
+        <v>122383513</v>
       </c>
       <c r="B17" t="n">
-        <v>90807</v>
+        <v>57379</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2414,34 +2420,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>563191</v>
+        <v>562901</v>
       </c>
       <c r="R17" t="n">
-        <v>7040857</v>
+        <v>7041298</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2473,7 +2484,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2483,7 +2494,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2510,10 +2526,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122383212</v>
+        <v>122381949</v>
       </c>
       <c r="B18" t="n">
-        <v>90807</v>
+        <v>79732</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2526,21 +2542,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2550,10 +2566,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>562931</v>
+        <v>563164</v>
       </c>
       <c r="R18" t="n">
-        <v>7041192</v>
+        <v>7040871</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2585,7 +2601,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2595,7 +2611,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2622,10 +2638,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122382243</v>
+        <v>122381544</v>
       </c>
       <c r="B19" t="n">
-        <v>78646</v>
+        <v>78651</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2662,10 +2678,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>563125</v>
+        <v>563309</v>
       </c>
       <c r="R19" t="n">
-        <v>7040906</v>
+        <v>7040893</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2697,7 +2713,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2707,7 +2723,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2734,10 +2750,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122382979</v>
+        <v>122382572</v>
       </c>
       <c r="B20" t="n">
-        <v>57374</v>
+        <v>98197</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2746,31 +2762,30 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2779,10 +2794,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>562944</v>
+        <v>563035</v>
       </c>
       <c r="R20" t="n">
-        <v>7041093</v>
+        <v>7040943</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2814,7 +2829,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2824,12 +2839,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:45</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2856,10 +2866,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122381566</v>
+        <v>122382726</v>
       </c>
       <c r="B21" t="n">
-        <v>82433</v>
+        <v>90819</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2872,21 +2882,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2896,10 +2906,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>563319</v>
+        <v>563044</v>
       </c>
       <c r="R21" t="n">
-        <v>7040899</v>
+        <v>7040945</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2931,7 +2941,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2941,7 +2951,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2968,10 +2978,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122384829</v>
+        <v>122383212</v>
       </c>
       <c r="B22" t="n">
-        <v>57374</v>
+        <v>90819</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2984,39 +2994,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>563205</v>
+        <v>562931</v>
       </c>
       <c r="R22" t="n">
-        <v>7040789</v>
+        <v>7041192</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3048,7 +3053,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3058,12 +3063,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:16</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3090,10 +3090,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122381544</v>
+        <v>122381532</v>
       </c>
       <c r="B23" t="n">
-        <v>78646</v>
+        <v>78651</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3130,10 +3130,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>563309</v>
+        <v>563324</v>
       </c>
       <c r="R23" t="n">
-        <v>7040893</v>
+        <v>7040908</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3165,7 +3165,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 57317-2024 artfynd.xlsx
+++ b/artfynd/A 57317-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122384637</v>
+        <v>122383513</v>
       </c>
       <c r="B2" t="n">
-        <v>90819</v>
+        <v>57379</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>563210</v>
+        <v>562901</v>
       </c>
       <c r="R2" t="n">
-        <v>7040790</v>
+        <v>7041298</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -904,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122384291</v>
+        <v>122382726</v>
       </c>
       <c r="B4" t="n">
-        <v>90819</v>
+        <v>90826</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -937,26 +947,17 @@
           <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563130</v>
+        <v>563044</v>
       </c>
       <c r="R4" t="n">
-        <v>7040874</v>
+        <v>7040945</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -988,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -998,7 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,22 +1014,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122381980</v>
+        <v>122382979</v>
       </c>
       <c r="B5" t="n">
-        <v>78651</v>
+        <v>57379</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1041,34 +1042,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563161</v>
+        <v>562944</v>
       </c>
       <c r="R5" t="n">
-        <v>7040863</v>
+        <v>7041093</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,7 +1106,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1110,7 +1116,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1137,10 +1148,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122381566</v>
+        <v>122384829</v>
       </c>
       <c r="B6" t="n">
-        <v>82438</v>
+        <v>57379</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1153,34 +1164,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563319</v>
+        <v>563205</v>
       </c>
       <c r="R6" t="n">
-        <v>7040899</v>
+        <v>7040789</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1212,7 +1228,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1222,7 +1238,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1249,10 +1270,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122382457</v>
+        <v>122384433</v>
       </c>
       <c r="B7" t="n">
-        <v>90801</v>
+        <v>57379</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1265,34 +1286,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>563028</v>
+        <v>563163</v>
       </c>
       <c r="R7" t="n">
-        <v>7040950</v>
+        <v>7040839</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1324,7 +1350,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1334,7 +1360,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1349,22 +1380,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122381802</v>
+        <v>122383248</v>
       </c>
       <c r="B8" t="n">
-        <v>90819</v>
+        <v>90826</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1401,10 +1432,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>563191</v>
+        <v>562917</v>
       </c>
       <c r="R8" t="n">
-        <v>7040857</v>
+        <v>7041224</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1436,7 +1467,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1446,7 +1477,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1473,10 +1504,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122384843</v>
+        <v>122384637</v>
       </c>
       <c r="B9" t="n">
-        <v>57395</v>
+        <v>90826</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1489,39 +1520,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>563208</v>
+        <v>563210</v>
       </c>
       <c r="R9" t="n">
-        <v>7040782</v>
+        <v>7040790</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1553,7 +1579,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1563,7 +1589,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1590,10 +1616,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122383327</v>
+        <v>122381544</v>
       </c>
       <c r="B10" t="n">
-        <v>90819</v>
+        <v>78651</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1606,21 +1632,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1630,10 +1656,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>562914</v>
+        <v>563309</v>
       </c>
       <c r="R10" t="n">
-        <v>7041282</v>
+        <v>7040893</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1665,7 +1691,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1675,7 +1701,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1702,10 +1728,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122384829</v>
+        <v>122381980</v>
       </c>
       <c r="B11" t="n">
-        <v>57379</v>
+        <v>78651</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1718,39 +1744,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>563205</v>
+        <v>563161</v>
       </c>
       <c r="R11" t="n">
-        <v>7040789</v>
+        <v>7040863</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1782,7 +1803,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1792,12 +1813,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:16</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1824,10 +1840,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122382979</v>
+        <v>122381566</v>
       </c>
       <c r="B12" t="n">
-        <v>57379</v>
+        <v>82438</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1840,39 +1856,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>562944</v>
+        <v>563319</v>
       </c>
       <c r="R12" t="n">
-        <v>7041093</v>
+        <v>7040899</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1904,7 +1915,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1914,12 +1925,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:45</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1946,10 +1952,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122383248</v>
+        <v>122383212</v>
       </c>
       <c r="B13" t="n">
-        <v>90819</v>
+        <v>90826</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1986,10 +1992,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>562917</v>
+        <v>562931</v>
       </c>
       <c r="R13" t="n">
-        <v>7041224</v>
+        <v>7041192</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2021,7 +2027,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2031,7 +2037,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2058,10 +2064,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122384433</v>
+        <v>122381532</v>
       </c>
       <c r="B14" t="n">
-        <v>57379</v>
+        <v>78651</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2074,39 +2080,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>563163</v>
+        <v>563324</v>
       </c>
       <c r="R14" t="n">
-        <v>7040839</v>
+        <v>7040908</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2138,7 +2139,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2148,12 +2149,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:52</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2168,22 +2164,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122382824</v>
+        <v>122381949</v>
       </c>
       <c r="B15" t="n">
-        <v>78651</v>
+        <v>79732</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2196,21 +2192,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2220,10 +2216,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>563010</v>
+        <v>563164</v>
       </c>
       <c r="R15" t="n">
-        <v>7041054</v>
+        <v>7040871</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2255,7 +2251,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2265,7 +2261,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2280,22 +2276,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122382243</v>
+        <v>122384291</v>
       </c>
       <c r="B16" t="n">
-        <v>78651</v>
+        <v>90826</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2308,34 +2304,43 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>563125</v>
+        <v>563130</v>
       </c>
       <c r="R16" t="n">
-        <v>7040906</v>
+        <v>7040874</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2367,7 +2372,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2377,7 +2382,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2392,22 +2397,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122383513</v>
+        <v>122382572</v>
       </c>
       <c r="B17" t="n">
-        <v>57379</v>
+        <v>98202</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2416,31 +2421,30 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2449,10 +2453,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>562901</v>
+        <v>563035</v>
       </c>
       <c r="R17" t="n">
-        <v>7041298</v>
+        <v>7040943</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2484,7 +2488,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2494,12 +2498,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:18</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2526,10 +2525,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122381949</v>
+        <v>122382457</v>
       </c>
       <c r="B18" t="n">
-        <v>79732</v>
+        <v>90808</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2542,21 +2541,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2566,10 +2565,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>563164</v>
+        <v>563028</v>
       </c>
       <c r="R18" t="n">
-        <v>7040871</v>
+        <v>7040950</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2601,7 +2600,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2611,7 +2610,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2638,10 +2637,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122381544</v>
+        <v>122381802</v>
       </c>
       <c r="B19" t="n">
-        <v>78651</v>
+        <v>90826</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2654,21 +2653,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2678,10 +2677,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>563309</v>
+        <v>563191</v>
       </c>
       <c r="R19" t="n">
-        <v>7040893</v>
+        <v>7040857</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2713,7 +2712,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2723,7 +2722,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2750,10 +2749,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122382572</v>
+        <v>122383327</v>
       </c>
       <c r="B20" t="n">
-        <v>98197</v>
+        <v>90826</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2762,42 +2761,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>563035</v>
+        <v>562914</v>
       </c>
       <c r="R20" t="n">
-        <v>7040943</v>
+        <v>7041282</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2829,7 +2824,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2839,7 +2834,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2866,10 +2861,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122382726</v>
+        <v>122382824</v>
       </c>
       <c r="B21" t="n">
-        <v>90819</v>
+        <v>78651</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2882,21 +2877,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2906,10 +2901,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>563044</v>
+        <v>563010</v>
       </c>
       <c r="R21" t="n">
-        <v>7040945</v>
+        <v>7041054</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2941,7 +2936,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2951,7 +2946,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2966,22 +2961,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122383212</v>
+        <v>122382243</v>
       </c>
       <c r="B22" t="n">
-        <v>90819</v>
+        <v>78651</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2994,21 +2989,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3018,10 +3013,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>562931</v>
+        <v>563125</v>
       </c>
       <c r="R22" t="n">
-        <v>7041192</v>
+        <v>7040906</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3053,7 +3048,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3063,7 +3058,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3090,10 +3085,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122381532</v>
+        <v>122384843</v>
       </c>
       <c r="B23" t="n">
-        <v>78651</v>
+        <v>57395</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3106,34 +3101,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>563324</v>
+        <v>563208</v>
       </c>
       <c r="R23" t="n">
-        <v>7040908</v>
+        <v>7040782</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3165,7 +3165,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 57317-2024 artfynd.xlsx
+++ b/artfynd/A 57317-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122383513</v>
+        <v>122383691</v>
       </c>
       <c r="B2" t="n">
-        <v>57379</v>
+        <v>57395</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -711,7 +711,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>562901</v>
+        <v>562911</v>
       </c>
       <c r="R2" t="n">
-        <v>7041298</v>
+        <v>7041237</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:18</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122383691</v>
+        <v>122383513</v>
       </c>
       <c r="B3" t="n">
-        <v>57395</v>
+        <v>57379</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,16 +808,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -833,7 +828,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -842,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>562911</v>
+        <v>562901</v>
       </c>
       <c r="R3" t="n">
-        <v>7041237</v>
+        <v>7041298</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,7 +882,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -2288,10 +2288,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122384291</v>
+        <v>122382572</v>
       </c>
       <c r="B16" t="n">
-        <v>90826</v>
+        <v>98202</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2300,25 +2300,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2326,21 +2326,16 @@
           <t>3</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>563130</v>
+        <v>563035</v>
       </c>
       <c r="R16" t="n">
-        <v>7040874</v>
+        <v>7040943</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2372,7 +2367,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2382,7 +2377,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2397,22 +2392,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122382572</v>
+        <v>122384291</v>
       </c>
       <c r="B17" t="n">
-        <v>98202</v>
+        <v>90826</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2421,25 +2416,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2447,16 +2442,21 @@
           <t>3</t>
         </is>
       </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>563035</v>
+        <v>563130</v>
       </c>
       <c r="R17" t="n">
-        <v>7040943</v>
+        <v>7040874</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2488,7 +2488,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2513,12 +2513,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>

--- a/artfynd/A 57317-2024 artfynd.xlsx
+++ b/artfynd/A 57317-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122383691</v>
+        <v>122383513</v>
       </c>
       <c r="B2" t="n">
-        <v>57395</v>
+        <v>57379</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -711,7 +711,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>562911</v>
+        <v>562901</v>
       </c>
       <c r="R2" t="n">
-        <v>7041237</v>
+        <v>7041298</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122383513</v>
+        <v>122383691</v>
       </c>
       <c r="B3" t="n">
-        <v>57379</v>
+        <v>57395</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,16 +813,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -828,7 +833,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -837,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>562901</v>
+        <v>562911</v>
       </c>
       <c r="R3" t="n">
-        <v>7041298</v>
+        <v>7041237</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,12 +887,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:18</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -2288,10 +2288,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122382572</v>
+        <v>122384291</v>
       </c>
       <c r="B16" t="n">
-        <v>98202</v>
+        <v>90826</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2300,25 +2300,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2326,16 +2326,21 @@
           <t>3</t>
         </is>
       </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>563035</v>
+        <v>563130</v>
       </c>
       <c r="R16" t="n">
-        <v>7040943</v>
+        <v>7040874</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2367,7 +2372,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2377,7 +2382,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2392,22 +2397,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122384291</v>
+        <v>122382572</v>
       </c>
       <c r="B17" t="n">
-        <v>90826</v>
+        <v>98202</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2416,25 +2421,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2442,21 +2447,16 @@
           <t>3</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>563130</v>
+        <v>563035</v>
       </c>
       <c r="R17" t="n">
-        <v>7040874</v>
+        <v>7040943</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2488,7 +2488,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2513,12 +2513,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>

--- a/artfynd/A 57317-2024 artfynd.xlsx
+++ b/artfynd/A 57317-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122383513</v>
+        <v>122383212</v>
       </c>
       <c r="B2" t="n">
-        <v>57379</v>
+        <v>90831</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,29 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>5432</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>562901</v>
+        <v>562931</v>
       </c>
       <c r="R2" t="n">
-        <v>7041298</v>
+        <v>7041192</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:18</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122383691</v>
+        <v>122381802</v>
       </c>
       <c r="B3" t="n">
-        <v>57395</v>
+        <v>90831</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,39 +798,29 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>5432</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>562911</v>
+        <v>563191</v>
       </c>
       <c r="R3" t="n">
-        <v>7041237</v>
+        <v>7040857</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122382726</v>
+        <v>122382979</v>
       </c>
       <c r="B4" t="n">
-        <v>90826</v>
+        <v>57379</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -930,34 +905,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
+        <v>100109</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563044</v>
+        <v>562944</v>
       </c>
       <c r="R4" t="n">
-        <v>7040945</v>
+        <v>7041093</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +974,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,7 +1006,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122382979</v>
+        <v>122384829</v>
       </c>
       <c r="B5" t="n">
         <v>57379</v>
@@ -1044,11 +1024,6 @@
       <c r="E5" t="n">
         <v>100109</v>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G5" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1062,7 +1037,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1071,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562944</v>
+        <v>563205</v>
       </c>
       <c r="R5" t="n">
-        <v>7041093</v>
+        <v>7040789</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1106,7 +1081,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1116,7 +1091,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1148,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122384829</v>
+        <v>122383327</v>
       </c>
       <c r="B6" t="n">
-        <v>57379</v>
+        <v>90831</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1164,39 +1139,29 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>5432</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563205</v>
+        <v>562914</v>
       </c>
       <c r="R6" t="n">
-        <v>7040789</v>
+        <v>7041282</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1228,7 +1193,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1238,12 +1203,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:16</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1270,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122384433</v>
+        <v>122381544</v>
       </c>
       <c r="B7" t="n">
-        <v>57379</v>
+        <v>78652</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1286,39 +1246,29 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>6425</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>563163</v>
+        <v>563309</v>
       </c>
       <c r="R7" t="n">
-        <v>7040839</v>
+        <v>7040893</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1350,7 +1300,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1360,12 +1310,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:52</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1380,22 +1325,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122383248</v>
+        <v>122382457</v>
       </c>
       <c r="B8" t="n">
-        <v>90826</v>
+        <v>90813</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1408,21 +1353,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
+        <v>1202</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1432,10 +1372,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>562917</v>
+        <v>563028</v>
       </c>
       <c r="R8" t="n">
-        <v>7041224</v>
+        <v>7040950</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1467,7 +1407,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1477,7 +1417,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1504,10 +1444,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122384637</v>
+        <v>122381532</v>
       </c>
       <c r="B9" t="n">
-        <v>90826</v>
+        <v>78652</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1520,21 +1460,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
+        <v>6425</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1544,10 +1479,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>563210</v>
+        <v>563324</v>
       </c>
       <c r="R9" t="n">
-        <v>7040790</v>
+        <v>7040908</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1579,7 +1514,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1589,7 +1524,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1616,10 +1551,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122381544</v>
+        <v>122381980</v>
       </c>
       <c r="B10" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1634,11 +1569,6 @@
       <c r="E10" t="n">
         <v>6425</v>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
       <c r="G10" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -1656,10 +1586,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>563309</v>
+        <v>563161</v>
       </c>
       <c r="R10" t="n">
-        <v>7040893</v>
+        <v>7040863</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1691,7 +1621,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1701,7 +1631,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1728,10 +1658,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122381980</v>
+        <v>122382572</v>
       </c>
       <c r="B11" t="n">
-        <v>78651</v>
+        <v>98211</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1740,38 +1670,37 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>220787</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>563161</v>
+        <v>563035</v>
       </c>
       <c r="R11" t="n">
-        <v>7040863</v>
+        <v>7040943</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1803,7 +1732,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1813,7 +1742,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1843,7 +1772,7 @@
         <v>122381566</v>
       </c>
       <c r="B12" t="n">
-        <v>82438</v>
+        <v>82439</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1857,11 +1786,6 @@
       </c>
       <c r="E12" t="n">
         <v>1312</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Gammelgransskål</t>
-        </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1952,10 +1876,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122383212</v>
+        <v>122384843</v>
       </c>
       <c r="B13" t="n">
-        <v>90826</v>
+        <v>57395</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1968,34 +1892,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
+        <v>100049</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>562931</v>
+        <v>563208</v>
       </c>
       <c r="R13" t="n">
-        <v>7041192</v>
+        <v>7040782</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2027,7 +1951,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2037,7 +1961,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2064,10 +1988,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122381532</v>
+        <v>122383691</v>
       </c>
       <c r="B14" t="n">
-        <v>78651</v>
+        <v>57395</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2080,34 +2004,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>100049</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>563324</v>
+        <v>562911</v>
       </c>
       <c r="R14" t="n">
-        <v>7040908</v>
+        <v>7041237</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2139,7 +2063,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2149,7 +2073,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2176,10 +2100,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122381949</v>
+        <v>122382726</v>
       </c>
       <c r="B15" t="n">
-        <v>79732</v>
+        <v>90831</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2192,21 +2116,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
+        <v>5432</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2216,10 +2135,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>563164</v>
+        <v>563044</v>
       </c>
       <c r="R15" t="n">
-        <v>7040871</v>
+        <v>7040945</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2251,7 +2170,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2261,7 +2180,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2288,10 +2207,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122384291</v>
+        <v>122383248</v>
       </c>
       <c r="B16" t="n">
-        <v>90826</v>
+        <v>90831</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2306,11 +2225,6 @@
       <c r="E16" t="n">
         <v>5432</v>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
       <c r="G16" t="inlineStr">
         <is>
           <t>Porodaedalea chrysoloma</t>
@@ -2321,26 +2235,17 @@
           <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>563130</v>
+        <v>562917</v>
       </c>
       <c r="R16" t="n">
-        <v>7040874</v>
+        <v>7041224</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2372,7 +2277,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2382,7 +2287,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2397,22 +2302,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122382572</v>
+        <v>122384637</v>
       </c>
       <c r="B17" t="n">
-        <v>98202</v>
+        <v>90831</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2421,42 +2326,33 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>5432</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>563035</v>
+        <v>563210</v>
       </c>
       <c r="R17" t="n">
-        <v>7040943</v>
+        <v>7040790</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2488,7 +2384,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2498,7 +2394,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2525,10 +2421,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122382457</v>
+        <v>122382824</v>
       </c>
       <c r="B18" t="n">
-        <v>90808</v>
+        <v>78652</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2541,21 +2437,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
+        <v>6425</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2565,10 +2456,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>563028</v>
+        <v>563010</v>
       </c>
       <c r="R18" t="n">
-        <v>7040950</v>
+        <v>7041054</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2600,7 +2491,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2610,7 +2501,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2625,22 +2516,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122381802</v>
+        <v>122381949</v>
       </c>
       <c r="B19" t="n">
-        <v>90826</v>
+        <v>79733</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2653,21 +2544,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
+        <v>6458</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2677,10 +2563,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>563191</v>
+        <v>563164</v>
       </c>
       <c r="R19" t="n">
-        <v>7040857</v>
+        <v>7040871</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2712,7 +2598,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2722,7 +2608,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2749,10 +2635,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122383327</v>
+        <v>122383513</v>
       </c>
       <c r="B20" t="n">
-        <v>90826</v>
+        <v>57379</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2765,34 +2651,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
+        <v>100109</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>562914</v>
+        <v>562901</v>
       </c>
       <c r="R20" t="n">
-        <v>7041282</v>
+        <v>7041298</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2824,7 +2710,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2834,7 +2720,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2861,10 +2752,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122382824</v>
+        <v>122384433</v>
       </c>
       <c r="B21" t="n">
-        <v>78651</v>
+        <v>57379</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2877,34 +2768,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>100109</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>563010</v>
+        <v>563163</v>
       </c>
       <c r="R21" t="n">
-        <v>7041054</v>
+        <v>7040839</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2936,7 +2827,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2946,7 +2837,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2973,10 +2869,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122382243</v>
+        <v>122384291</v>
       </c>
       <c r="B22" t="n">
-        <v>78651</v>
+        <v>90831</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2989,34 +2885,38 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>5432</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>563125</v>
+        <v>563130</v>
       </c>
       <c r="R22" t="n">
-        <v>7040906</v>
+        <v>7040874</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3048,7 +2948,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3058,7 +2958,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3073,22 +2973,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122384843</v>
+        <v>122382243</v>
       </c>
       <c r="B23" t="n">
-        <v>57395</v>
+        <v>78652</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3101,39 +3001,29 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>6425</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>563208</v>
+        <v>563125</v>
       </c>
       <c r="R23" t="n">
-        <v>7040782</v>
+        <v>7040906</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3165,7 +3055,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3175,7 +3065,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 57317-2024 artfynd.xlsx
+++ b/artfynd/A 57317-2024 artfynd.xlsx
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122382979</v>
+        <v>122383327</v>
       </c>
       <c r="B4" t="n">
-        <v>57379</v>
+        <v>90831</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,34 +905,29 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562944</v>
+        <v>562914</v>
       </c>
       <c r="R4" t="n">
-        <v>7041093</v>
+        <v>7041282</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -974,12 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:45</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122384829</v>
+        <v>122381544</v>
       </c>
       <c r="B5" t="n">
-        <v>57379</v>
+        <v>78652</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1022,34 +1012,29 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563205</v>
+        <v>563309</v>
       </c>
       <c r="R5" t="n">
-        <v>7040789</v>
+        <v>7040893</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1081,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1091,12 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:16</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122383327</v>
+        <v>122382979</v>
       </c>
       <c r="B6" t="n">
-        <v>90831</v>
+        <v>57379</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,29 +1119,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>562914</v>
+        <v>562944</v>
       </c>
       <c r="R6" t="n">
-        <v>7041282</v>
+        <v>7041093</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1193,7 +1178,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1203,7 +1188,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1230,10 +1220,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122381544</v>
+        <v>122384829</v>
       </c>
       <c r="B7" t="n">
-        <v>78652</v>
+        <v>57379</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1246,29 +1236,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>563309</v>
+        <v>563205</v>
       </c>
       <c r="R7" t="n">
-        <v>7040893</v>
+        <v>7040789</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1300,7 +1295,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1310,7 +1305,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 57317-2024 artfynd.xlsx
+++ b/artfynd/A 57317-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122383212</v>
+        <v>122382572</v>
       </c>
       <c r="B2" t="n">
-        <v>90831</v>
+        <v>98224</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,33 +687,42 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>220787</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>562931</v>
+        <v>563035</v>
       </c>
       <c r="R2" t="n">
-        <v>7041192</v>
+        <v>7040943</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122381802</v>
+        <v>122381532</v>
       </c>
       <c r="B3" t="n">
-        <v>90831</v>
+        <v>78656</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,16 +807,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>6425</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563191</v>
+        <v>563324</v>
       </c>
       <c r="R3" t="n">
-        <v>7040857</v>
+        <v>7040908</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +876,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122383327</v>
+        <v>122384829</v>
       </c>
       <c r="B4" t="n">
-        <v>90831</v>
+        <v>57383</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,29 +919,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>100109</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562914</v>
+        <v>563205</v>
       </c>
       <c r="R4" t="n">
-        <v>7041282</v>
+        <v>7040789</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +993,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +1025,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122381544</v>
+        <v>122382979</v>
       </c>
       <c r="B5" t="n">
-        <v>78652</v>
+        <v>57383</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,29 +1041,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563309</v>
+        <v>562944</v>
       </c>
       <c r="R5" t="n">
-        <v>7040893</v>
+        <v>7041093</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1105,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1115,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1147,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122382979</v>
+        <v>122384843</v>
       </c>
       <c r="B6" t="n">
-        <v>57379</v>
+        <v>57399</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1119,11 +1163,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>100049</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1134,7 +1183,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1143,10 +1192,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>562944</v>
+        <v>563208</v>
       </c>
       <c r="R6" t="n">
-        <v>7041093</v>
+        <v>7040782</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1227,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1188,12 +1237,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:45</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,10 +1264,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122384829</v>
+        <v>122382457</v>
       </c>
       <c r="B7" t="n">
-        <v>57379</v>
+        <v>90826</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1236,34 +1280,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>1202</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>563205</v>
+        <v>563028</v>
       </c>
       <c r="R7" t="n">
-        <v>7040789</v>
+        <v>7040950</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1295,7 +1339,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1305,12 +1349,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:16</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1337,10 +1376,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122382457</v>
+        <v>122383691</v>
       </c>
       <c r="B8" t="n">
-        <v>90813</v>
+        <v>57399</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1353,29 +1392,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>100049</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>563028</v>
+        <v>562911</v>
       </c>
       <c r="R8" t="n">
-        <v>7040950</v>
+        <v>7041237</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1407,7 +1456,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1417,7 +1466,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1444,10 +1493,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122381532</v>
+        <v>122381802</v>
       </c>
       <c r="B9" t="n">
-        <v>78652</v>
+        <v>90844</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1460,16 +1509,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>5432</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1479,10 +1533,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>563324</v>
+        <v>563191</v>
       </c>
       <c r="R9" t="n">
-        <v>7040908</v>
+        <v>7040857</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1514,7 +1568,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1524,7 +1578,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1551,10 +1605,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122381980</v>
+        <v>122382824</v>
       </c>
       <c r="B10" t="n">
-        <v>78652</v>
+        <v>78656</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1569,6 +1623,11 @@
       <c r="E10" t="n">
         <v>6425</v>
       </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
       <c r="G10" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -1586,10 +1645,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>563161</v>
+        <v>563010</v>
       </c>
       <c r="R10" t="n">
-        <v>7040863</v>
+        <v>7041054</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1621,7 +1680,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1631,7 +1690,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1646,22 +1705,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122382572</v>
+        <v>122384291</v>
       </c>
       <c r="B11" t="n">
-        <v>98211</v>
+        <v>90844</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1670,20 +1729,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>5432</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1691,16 +1755,21 @@
           <t>3</t>
         </is>
       </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>563035</v>
+        <v>563130</v>
       </c>
       <c r="R11" t="n">
-        <v>7040943</v>
+        <v>7040874</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1732,7 +1801,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1742,7 +1811,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1757,22 +1826,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122381566</v>
+        <v>122381949</v>
       </c>
       <c r="B12" t="n">
-        <v>82439</v>
+        <v>79737</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1785,16 +1854,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1312</v>
+        <v>6458</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1804,10 +1878,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>563319</v>
+        <v>563164</v>
       </c>
       <c r="R12" t="n">
-        <v>7040899</v>
+        <v>7040871</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1839,7 +1913,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1849,7 +1923,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1876,10 +1950,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122384843</v>
+        <v>122381980</v>
       </c>
       <c r="B13" t="n">
-        <v>57395</v>
+        <v>78656</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1892,34 +1966,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>563208</v>
+        <v>563161</v>
       </c>
       <c r="R13" t="n">
-        <v>7040782</v>
+        <v>7040863</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1951,7 +2025,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1961,7 +2035,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1988,10 +2062,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122383691</v>
+        <v>122381566</v>
       </c>
       <c r="B14" t="n">
-        <v>57395</v>
+        <v>82443</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2004,34 +2078,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>1312</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>562911</v>
+        <v>563319</v>
       </c>
       <c r="R14" t="n">
-        <v>7041237</v>
+        <v>7040899</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2063,7 +2137,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2073,7 +2147,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2100,10 +2174,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122382726</v>
+        <v>122383212</v>
       </c>
       <c r="B15" t="n">
-        <v>90831</v>
+        <v>90844</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2118,6 +2192,11 @@
       <c r="E15" t="n">
         <v>5432</v>
       </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
       <c r="G15" t="inlineStr">
         <is>
           <t>Porodaedalea chrysoloma</t>
@@ -2135,10 +2214,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>563044</v>
+        <v>562931</v>
       </c>
       <c r="R15" t="n">
-        <v>7040945</v>
+        <v>7041192</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2170,7 +2249,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2180,7 +2259,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2210,7 +2289,7 @@
         <v>122383248</v>
       </c>
       <c r="B16" t="n">
-        <v>90831</v>
+        <v>90844</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2224,6 +2303,11 @@
       </c>
       <c r="E16" t="n">
         <v>5432</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -2314,10 +2398,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122384637</v>
+        <v>122382243</v>
       </c>
       <c r="B17" t="n">
-        <v>90831</v>
+        <v>78656</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2330,16 +2414,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>6425</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2349,10 +2438,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>563210</v>
+        <v>563125</v>
       </c>
       <c r="R17" t="n">
-        <v>7040790</v>
+        <v>7040906</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2384,7 +2473,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2394,7 +2483,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2421,10 +2510,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122382824</v>
+        <v>122383513</v>
       </c>
       <c r="B18" t="n">
-        <v>78652</v>
+        <v>57383</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2437,29 +2526,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>563010</v>
+        <v>562901</v>
       </c>
       <c r="R18" t="n">
-        <v>7041054</v>
+        <v>7041298</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2491,7 +2590,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2501,7 +2600,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2516,22 +2620,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122381949</v>
+        <v>122381544</v>
       </c>
       <c r="B19" t="n">
-        <v>79733</v>
+        <v>78656</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2544,16 +2648,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>6425</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2563,10 +2672,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>563164</v>
+        <v>563309</v>
       </c>
       <c r="R19" t="n">
-        <v>7040871</v>
+        <v>7040893</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2598,7 +2707,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2608,7 +2717,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2635,10 +2744,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122383513</v>
+        <v>122384637</v>
       </c>
       <c r="B20" t="n">
-        <v>57379</v>
+        <v>90844</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2651,34 +2760,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>5432</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>562901</v>
+        <v>563210</v>
       </c>
       <c r="R20" t="n">
-        <v>7041298</v>
+        <v>7040790</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2710,7 +2819,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2720,12 +2829,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:18</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2752,10 +2856,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122384433</v>
+        <v>122382726</v>
       </c>
       <c r="B21" t="n">
-        <v>57379</v>
+        <v>90844</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2768,34 +2872,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>5432</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>563163</v>
+        <v>563044</v>
       </c>
       <c r="R21" t="n">
-        <v>7040839</v>
+        <v>7040945</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2827,7 +2931,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2837,12 +2941,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:52</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2857,22 +2956,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122384291</v>
+        <v>122383327</v>
       </c>
       <c r="B22" t="n">
-        <v>90831</v>
+        <v>90844</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2887,6 +2986,11 @@
       <c r="E22" t="n">
         <v>5432</v>
       </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
       <c r="G22" t="inlineStr">
         <is>
           <t>Porodaedalea chrysoloma</t>
@@ -2897,26 +3001,17 @@
           <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>563130</v>
+        <v>562914</v>
       </c>
       <c r="R22" t="n">
-        <v>7040874</v>
+        <v>7041282</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2948,7 +3043,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2958,7 +3053,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2973,22 +3068,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122382243</v>
+        <v>122384433</v>
       </c>
       <c r="B23" t="n">
-        <v>78652</v>
+        <v>57383</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3001,29 +3096,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>563125</v>
+        <v>563163</v>
       </c>
       <c r="R23" t="n">
-        <v>7040906</v>
+        <v>7040839</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3055,7 +3160,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3065,7 +3170,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3080,12 +3190,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>

--- a/artfynd/A 57317-2024 artfynd.xlsx
+++ b/artfynd/A 57317-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122382572</v>
       </c>
       <c r="B2" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122381532</v>
+        <v>122382243</v>
       </c>
       <c r="B3" t="n">
         <v>78656</v>
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563324</v>
+        <v>563125</v>
       </c>
       <c r="R3" t="n">
-        <v>7040908</v>
+        <v>7040906</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122384829</v>
+        <v>122381532</v>
       </c>
       <c r="B4" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,39 +919,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563205</v>
+        <v>563324</v>
       </c>
       <c r="R4" t="n">
-        <v>7040789</v>
+        <v>7040908</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -983,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,12 +988,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:16</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122382979</v>
+        <v>122382457</v>
       </c>
       <c r="B5" t="n">
-        <v>57383</v>
+        <v>90839</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1041,39 +1031,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562944</v>
+        <v>563028</v>
       </c>
       <c r="R5" t="n">
-        <v>7041093</v>
+        <v>7040950</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1105,7 +1090,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1115,12 +1100,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:45</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1147,10 +1127,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122384843</v>
+        <v>122384637</v>
       </c>
       <c r="B6" t="n">
-        <v>57399</v>
+        <v>90857</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1163,39 +1143,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563208</v>
+        <v>563210</v>
       </c>
       <c r="R6" t="n">
-        <v>7040782</v>
+        <v>7040790</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1227,7 +1202,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1237,7 +1212,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1264,10 +1239,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122382457</v>
+        <v>122381544</v>
       </c>
       <c r="B7" t="n">
-        <v>90826</v>
+        <v>78656</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1280,21 +1255,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1304,10 +1279,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>563028</v>
+        <v>563309</v>
       </c>
       <c r="R7" t="n">
-        <v>7040950</v>
+        <v>7040893</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1339,7 +1314,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1349,7 +1324,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1376,10 +1351,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122383691</v>
+        <v>122384433</v>
       </c>
       <c r="B8" t="n">
-        <v>57399</v>
+        <v>57383</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1392,16 +1367,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1421,10 +1396,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>562911</v>
+        <v>563163</v>
       </c>
       <c r="R8" t="n">
-        <v>7041237</v>
+        <v>7040839</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1456,7 +1431,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1466,7 +1441,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1481,22 +1461,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122381802</v>
+        <v>122383212</v>
       </c>
       <c r="B9" t="n">
-        <v>90844</v>
+        <v>90857</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1533,10 +1513,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>563191</v>
+        <v>562931</v>
       </c>
       <c r="R9" t="n">
-        <v>7040857</v>
+        <v>7041192</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1568,7 +1548,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1578,7 +1558,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1605,10 +1585,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122382824</v>
+        <v>122381566</v>
       </c>
       <c r="B10" t="n">
-        <v>78656</v>
+        <v>82443</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1621,21 +1601,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1645,10 +1625,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>563010</v>
+        <v>563319</v>
       </c>
       <c r="R10" t="n">
-        <v>7041054</v>
+        <v>7040899</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1680,7 +1660,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1690,7 +1670,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1705,22 +1685,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122384291</v>
+        <v>122383327</v>
       </c>
       <c r="B11" t="n">
-        <v>90844</v>
+        <v>90857</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1750,26 +1730,17 @@
           <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>563130</v>
+        <v>562914</v>
       </c>
       <c r="R11" t="n">
-        <v>7040874</v>
+        <v>7041282</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1801,7 +1772,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1811,7 +1782,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1826,22 +1797,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122381949</v>
+        <v>122382979</v>
       </c>
       <c r="B12" t="n">
-        <v>79737</v>
+        <v>57383</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1854,34 +1825,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>563164</v>
+        <v>562944</v>
       </c>
       <c r="R12" t="n">
-        <v>7040871</v>
+        <v>7041093</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1913,7 +1889,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1923,7 +1899,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1950,10 +1931,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122381980</v>
+        <v>122381802</v>
       </c>
       <c r="B13" t="n">
-        <v>78656</v>
+        <v>90857</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1966,21 +1947,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1990,10 +1971,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>563161</v>
+        <v>563191</v>
       </c>
       <c r="R13" t="n">
-        <v>7040863</v>
+        <v>7040857</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2025,7 +2006,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2035,7 +2016,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2062,10 +2043,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122381566</v>
+        <v>122383248</v>
       </c>
       <c r="B14" t="n">
-        <v>82443</v>
+        <v>90857</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2078,21 +2059,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2102,10 +2083,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>563319</v>
+        <v>562917</v>
       </c>
       <c r="R14" t="n">
-        <v>7040899</v>
+        <v>7041224</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2137,7 +2118,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2147,7 +2128,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2174,10 +2155,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122383212</v>
+        <v>122384291</v>
       </c>
       <c r="B15" t="n">
-        <v>90844</v>
+        <v>90857</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2207,17 +2188,26 @@
           <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>562931</v>
+        <v>563130</v>
       </c>
       <c r="R15" t="n">
-        <v>7041192</v>
+        <v>7040874</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2249,7 +2239,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2259,7 +2249,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2274,22 +2264,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122383248</v>
+        <v>122381980</v>
       </c>
       <c r="B16" t="n">
-        <v>90844</v>
+        <v>78656</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2302,21 +2292,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2326,10 +2316,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>562917</v>
+        <v>563161</v>
       </c>
       <c r="R16" t="n">
-        <v>7041224</v>
+        <v>7040863</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2361,7 +2351,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2371,7 +2361,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2398,10 +2388,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122382243</v>
+        <v>122383691</v>
       </c>
       <c r="B17" t="n">
-        <v>78656</v>
+        <v>57399</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2414,34 +2404,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>563125</v>
+        <v>562911</v>
       </c>
       <c r="R17" t="n">
-        <v>7040906</v>
+        <v>7041237</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2473,7 +2468,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2483,7 +2478,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2510,10 +2505,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122383513</v>
+        <v>122384843</v>
       </c>
       <c r="B18" t="n">
-        <v>57383</v>
+        <v>57399</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2526,16 +2521,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2546,7 +2541,7 @@
       <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2555,10 +2550,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>562901</v>
+        <v>563208</v>
       </c>
       <c r="R18" t="n">
-        <v>7041298</v>
+        <v>7040782</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2590,7 +2585,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2600,12 +2595,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:18</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2632,10 +2622,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122381544</v>
+        <v>122381949</v>
       </c>
       <c r="B19" t="n">
-        <v>78656</v>
+        <v>79737</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2648,21 +2638,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2672,10 +2662,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>563309</v>
+        <v>563164</v>
       </c>
       <c r="R19" t="n">
-        <v>7040893</v>
+        <v>7040871</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2707,7 +2697,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2717,7 +2707,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2744,10 +2734,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122384637</v>
+        <v>122382824</v>
       </c>
       <c r="B20" t="n">
-        <v>90844</v>
+        <v>78656</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2760,21 +2750,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2784,10 +2774,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>563210</v>
+        <v>563010</v>
       </c>
       <c r="R20" t="n">
-        <v>7040790</v>
+        <v>7041054</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2819,7 +2809,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2829,7 +2819,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2844,22 +2834,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122382726</v>
+        <v>122384829</v>
       </c>
       <c r="B21" t="n">
-        <v>90844</v>
+        <v>57383</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2872,34 +2862,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>563044</v>
+        <v>563205</v>
       </c>
       <c r="R21" t="n">
-        <v>7040945</v>
+        <v>7040789</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2931,7 +2926,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2941,7 +2936,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2968,10 +2968,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122383327</v>
+        <v>122383513</v>
       </c>
       <c r="B22" t="n">
-        <v>90844</v>
+        <v>57383</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2984,34 +2984,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>562914</v>
+        <v>562901</v>
       </c>
       <c r="R22" t="n">
-        <v>7041282</v>
+        <v>7041298</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3043,7 +3048,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3053,7 +3058,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3080,10 +3090,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122384433</v>
+        <v>122382726</v>
       </c>
       <c r="B23" t="n">
-        <v>57383</v>
+        <v>90857</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3096,39 +3106,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>563163</v>
+        <v>563044</v>
       </c>
       <c r="R23" t="n">
-        <v>7040839</v>
+        <v>7040945</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3160,7 +3165,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3170,12 +3175,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:52</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3190,12 +3190,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>

--- a/artfynd/A 57317-2024 artfynd.xlsx
+++ b/artfynd/A 57317-2024 artfynd.xlsx
@@ -1015,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122382457</v>
+        <v>122384637</v>
       </c>
       <c r="B5" t="n">
-        <v>90839</v>
+        <v>90857</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1031,21 +1031,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1055,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563028</v>
+        <v>563210</v>
       </c>
       <c r="R5" t="n">
-        <v>7040950</v>
+        <v>7040790</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1090,7 +1090,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1100,7 +1100,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,10 +1127,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122384637</v>
+        <v>122381544</v>
       </c>
       <c r="B6" t="n">
-        <v>90857</v>
+        <v>78656</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,21 +1143,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563210</v>
+        <v>563309</v>
       </c>
       <c r="R6" t="n">
-        <v>7040790</v>
+        <v>7040893</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1239,10 +1239,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122381544</v>
+        <v>122382457</v>
       </c>
       <c r="B7" t="n">
-        <v>78656</v>
+        <v>90839</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1255,21 +1255,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1279,10 +1279,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>563309</v>
+        <v>563028</v>
       </c>
       <c r="R7" t="n">
-        <v>7040893</v>
+        <v>7040950</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -2276,10 +2276,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122381980</v>
+        <v>122383691</v>
       </c>
       <c r="B16" t="n">
-        <v>78656</v>
+        <v>57399</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2292,34 +2292,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>563161</v>
+        <v>562911</v>
       </c>
       <c r="R16" t="n">
-        <v>7040863</v>
+        <v>7041237</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2351,7 +2356,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2361,7 +2366,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2388,10 +2393,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122383691</v>
+        <v>122381980</v>
       </c>
       <c r="B17" t="n">
-        <v>57399</v>
+        <v>78656</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2404,39 +2409,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>562911</v>
+        <v>563161</v>
       </c>
       <c r="R17" t="n">
-        <v>7041237</v>
+        <v>7040863</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2478,7 +2478,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 57317-2024 artfynd.xlsx
+++ b/artfynd/A 57317-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122382572</v>
+        <v>122383212</v>
       </c>
       <c r="B2" t="n">
-        <v>98237</v>
+        <v>90857</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,42 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>563035</v>
+        <v>562931</v>
       </c>
       <c r="R2" t="n">
-        <v>7040943</v>
+        <v>7041192</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122382243</v>
+        <v>122383327</v>
       </c>
       <c r="B3" t="n">
-        <v>78656</v>
+        <v>90857</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563125</v>
+        <v>562914</v>
       </c>
       <c r="R3" t="n">
-        <v>7040906</v>
+        <v>7041282</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122381532</v>
+        <v>122381802</v>
       </c>
       <c r="B4" t="n">
-        <v>78656</v>
+        <v>90857</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -943,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563324</v>
+        <v>563191</v>
       </c>
       <c r="R4" t="n">
-        <v>7040908</v>
+        <v>7040857</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1015,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122384637</v>
+        <v>122382979</v>
       </c>
       <c r="B5" t="n">
-        <v>90857</v>
+        <v>57383</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1031,34 +1027,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563210</v>
+        <v>562944</v>
       </c>
       <c r="R5" t="n">
-        <v>7040790</v>
+        <v>7041093</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1090,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1100,7 +1101,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122381544</v>
+        <v>122384829</v>
       </c>
       <c r="B6" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,34 +1149,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563309</v>
+        <v>563205</v>
       </c>
       <c r="R6" t="n">
-        <v>7040893</v>
+        <v>7040789</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1202,7 +1213,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1212,7 +1223,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1239,10 +1255,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122382457</v>
+        <v>122382824</v>
       </c>
       <c r="B7" t="n">
-        <v>90839</v>
+        <v>78656</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1255,21 +1271,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1279,10 +1295,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>563028</v>
+        <v>563010</v>
       </c>
       <c r="R7" t="n">
-        <v>7040950</v>
+        <v>7041054</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1314,7 +1330,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1324,7 +1340,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1339,22 +1355,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122384433</v>
+        <v>122382243</v>
       </c>
       <c r="B8" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1367,39 +1383,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>563163</v>
+        <v>563125</v>
       </c>
       <c r="R8" t="n">
-        <v>7040839</v>
+        <v>7040906</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1431,7 +1442,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1441,12 +1452,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:52</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1461,19 +1467,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122383212</v>
+        <v>122382726</v>
       </c>
       <c r="B9" t="n">
         <v>90857</v>
@@ -1513,10 +1519,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>562931</v>
+        <v>563044</v>
       </c>
       <c r="R9" t="n">
-        <v>7041192</v>
+        <v>7040945</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1548,7 +1554,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1558,7 +1564,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1585,10 +1591,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122381566</v>
+        <v>122384843</v>
       </c>
       <c r="B10" t="n">
-        <v>82443</v>
+        <v>57399</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1601,34 +1607,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>563319</v>
+        <v>563208</v>
       </c>
       <c r="R10" t="n">
-        <v>7040899</v>
+        <v>7040782</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1660,7 +1671,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1670,7 +1681,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1697,10 +1708,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122383327</v>
+        <v>122381949</v>
       </c>
       <c r="B11" t="n">
-        <v>90857</v>
+        <v>79737</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1713,21 +1724,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1737,10 +1748,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>562914</v>
+        <v>563164</v>
       </c>
       <c r="R11" t="n">
-        <v>7041282</v>
+        <v>7040871</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1772,7 +1783,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1782,7 +1793,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1809,10 +1820,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122382979</v>
+        <v>122383691</v>
       </c>
       <c r="B12" t="n">
-        <v>57383</v>
+        <v>57399</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1825,16 +1836,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1845,7 +1856,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1854,10 +1865,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>562944</v>
+        <v>562911</v>
       </c>
       <c r="R12" t="n">
-        <v>7041093</v>
+        <v>7041237</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1889,7 +1900,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1899,12 +1910,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:45</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1931,10 +1937,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122381802</v>
+        <v>122382457</v>
       </c>
       <c r="B13" t="n">
-        <v>90857</v>
+        <v>90839</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1947,21 +1953,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1971,10 +1977,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>563191</v>
+        <v>563028</v>
       </c>
       <c r="R13" t="n">
-        <v>7040857</v>
+        <v>7040950</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2006,7 +2012,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2016,7 +2022,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2043,10 +2049,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122383248</v>
+        <v>122381532</v>
       </c>
       <c r="B14" t="n">
-        <v>90857</v>
+        <v>78656</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2059,21 +2065,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2083,10 +2089,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>562917</v>
+        <v>563324</v>
       </c>
       <c r="R14" t="n">
-        <v>7041224</v>
+        <v>7040908</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2118,7 +2124,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2128,7 +2134,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2155,7 +2161,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122384291</v>
+        <v>122384637</v>
       </c>
       <c r="B15" t="n">
         <v>90857</v>
@@ -2188,26 +2194,17 @@
           <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>563130</v>
+        <v>563210</v>
       </c>
       <c r="R15" t="n">
-        <v>7040874</v>
+        <v>7040790</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2239,7 +2236,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2249,7 +2246,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2264,22 +2261,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122383691</v>
+        <v>122383248</v>
       </c>
       <c r="B16" t="n">
-        <v>57399</v>
+        <v>90857</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2292,39 +2289,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>562911</v>
+        <v>562917</v>
       </c>
       <c r="R16" t="n">
-        <v>7041237</v>
+        <v>7041224</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2356,7 +2348,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2366,7 +2358,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2505,10 +2497,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122384843</v>
+        <v>122383513</v>
       </c>
       <c r="B18" t="n">
-        <v>57399</v>
+        <v>57383</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2521,16 +2513,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2541,7 +2533,7 @@
       <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2550,10 +2542,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>563208</v>
+        <v>562901</v>
       </c>
       <c r="R18" t="n">
-        <v>7040782</v>
+        <v>7041298</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2585,7 +2577,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2595,7 +2587,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2622,10 +2619,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122381949</v>
+        <v>122381544</v>
       </c>
       <c r="B19" t="n">
-        <v>79737</v>
+        <v>78656</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2638,21 +2635,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2662,10 +2659,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>563164</v>
+        <v>563309</v>
       </c>
       <c r="R19" t="n">
-        <v>7040871</v>
+        <v>7040893</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2697,7 +2694,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2707,7 +2704,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2734,10 +2731,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122382824</v>
+        <v>122384433</v>
       </c>
       <c r="B20" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2750,34 +2747,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>563010</v>
+        <v>563163</v>
       </c>
       <c r="R20" t="n">
-        <v>7041054</v>
+        <v>7040839</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2809,7 +2811,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2819,7 +2821,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2846,10 +2853,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122384829</v>
+        <v>122381566</v>
       </c>
       <c r="B21" t="n">
-        <v>57383</v>
+        <v>82443</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2862,39 +2869,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>563205</v>
+        <v>563319</v>
       </c>
       <c r="R21" t="n">
-        <v>7040789</v>
+        <v>7040899</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2926,7 +2928,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2936,12 +2938,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:16</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2968,10 +2965,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122383513</v>
+        <v>122382572</v>
       </c>
       <c r="B22" t="n">
-        <v>57383</v>
+        <v>98237</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2980,31 +2977,30 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3013,10 +3009,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>562901</v>
+        <v>563035</v>
       </c>
       <c r="R22" t="n">
-        <v>7041298</v>
+        <v>7040943</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3048,7 +3044,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3058,12 +3054,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:18</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3090,7 +3081,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122382726</v>
+        <v>122384291</v>
       </c>
       <c r="B23" t="n">
         <v>90857</v>
@@ -3123,17 +3114,26 @@
           <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>563044</v>
+        <v>563130</v>
       </c>
       <c r="R23" t="n">
-        <v>7040945</v>
+        <v>7040874</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3165,7 +3165,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3190,12 +3190,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>

--- a/artfynd/A 57317-2024 artfynd.xlsx
+++ b/artfynd/A 57317-2024 artfynd.xlsx
@@ -1708,10 +1708,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122381949</v>
+        <v>122383691</v>
       </c>
       <c r="B11" t="n">
-        <v>79737</v>
+        <v>57399</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1724,34 +1724,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>563164</v>
+        <v>562911</v>
       </c>
       <c r="R11" t="n">
-        <v>7040871</v>
+        <v>7041237</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1783,7 +1788,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1793,7 +1798,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1820,10 +1825,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122383691</v>
+        <v>122381949</v>
       </c>
       <c r="B12" t="n">
-        <v>57399</v>
+        <v>79737</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1836,39 +1841,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>562911</v>
+        <v>563164</v>
       </c>
       <c r="R12" t="n">
-        <v>7041237</v>
+        <v>7040871</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1937,10 +1937,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122382457</v>
+        <v>122381532</v>
       </c>
       <c r="B13" t="n">
-        <v>90839</v>
+        <v>78656</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1953,21 +1953,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1977,10 +1977,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>563028</v>
+        <v>563324</v>
       </c>
       <c r="R13" t="n">
-        <v>7040950</v>
+        <v>7040908</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2012,7 +2012,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2022,7 +2022,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2049,10 +2049,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122381532</v>
+        <v>122382457</v>
       </c>
       <c r="B14" t="n">
-        <v>78656</v>
+        <v>90839</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2065,21 +2065,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2089,10 +2089,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>563324</v>
+        <v>563028</v>
       </c>
       <c r="R14" t="n">
-        <v>7040908</v>
+        <v>7040950</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2124,7 +2124,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 57317-2024 artfynd.xlsx
+++ b/artfynd/A 57317-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122383212</v>
+        <v>122383248</v>
       </c>
       <c r="B2" t="n">
-        <v>90857</v>
+        <v>90851</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>562931</v>
+        <v>562917</v>
       </c>
       <c r="R2" t="n">
-        <v>7041192</v>
+        <v>7041224</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122383327</v>
+        <v>122381544</v>
       </c>
       <c r="B3" t="n">
-        <v>90857</v>
+        <v>78656</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>562914</v>
+        <v>563309</v>
       </c>
       <c r="R3" t="n">
-        <v>7041282</v>
+        <v>7040893</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122381802</v>
+        <v>122382979</v>
       </c>
       <c r="B4" t="n">
-        <v>90857</v>
+        <v>57383</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,34 +915,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563191</v>
+        <v>562944</v>
       </c>
       <c r="R4" t="n">
-        <v>7040857</v>
+        <v>7041093</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +989,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,7 +1021,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122382979</v>
+        <v>122384433</v>
       </c>
       <c r="B5" t="n">
         <v>57383</v>
@@ -1047,7 +1057,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1056,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562944</v>
+        <v>563163</v>
       </c>
       <c r="R5" t="n">
-        <v>7041093</v>
+        <v>7040839</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,12 +1111,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1121,22 +1131,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122384829</v>
+        <v>122381566</v>
       </c>
       <c r="B6" t="n">
-        <v>57383</v>
+        <v>82443</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,39 +1159,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563205</v>
+        <v>563319</v>
       </c>
       <c r="R6" t="n">
-        <v>7040789</v>
+        <v>7040899</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,7 +1218,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,12 +1228,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:16</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,10 +1255,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122382824</v>
+        <v>122381802</v>
       </c>
       <c r="B7" t="n">
-        <v>78656</v>
+        <v>90851</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1271,21 +1271,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1295,10 +1295,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>563010</v>
+        <v>563191</v>
       </c>
       <c r="R7" t="n">
-        <v>7041054</v>
+        <v>7040857</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1330,7 +1330,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1340,7 +1340,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1355,22 +1355,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122382243</v>
+        <v>122382726</v>
       </c>
       <c r="B8" t="n">
-        <v>78656</v>
+        <v>90851</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1383,21 +1383,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1407,10 +1407,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>563125</v>
+        <v>563044</v>
       </c>
       <c r="R8" t="n">
-        <v>7040906</v>
+        <v>7040945</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1442,7 +1442,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1479,10 +1479,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122382726</v>
+        <v>122382243</v>
       </c>
       <c r="B9" t="n">
-        <v>90857</v>
+        <v>78656</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1495,21 +1495,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1519,10 +1519,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>563044</v>
+        <v>563125</v>
       </c>
       <c r="R9" t="n">
-        <v>7040945</v>
+        <v>7040906</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1554,7 +1554,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1591,10 +1591,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122384843</v>
+        <v>122384829</v>
       </c>
       <c r="B10" t="n">
-        <v>57399</v>
+        <v>57383</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1607,16 +1607,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1636,10 +1636,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>563208</v>
+        <v>563205</v>
       </c>
       <c r="R10" t="n">
-        <v>7040782</v>
+        <v>7040789</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1681,7 +1681,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1708,10 +1713,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122383691</v>
+        <v>122384291</v>
       </c>
       <c r="B11" t="n">
-        <v>57399</v>
+        <v>90851</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1724,27 +1729,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1753,10 +1762,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>562911</v>
+        <v>563130</v>
       </c>
       <c r="R11" t="n">
-        <v>7041237</v>
+        <v>7040874</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1788,7 +1797,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1798,7 +1807,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1813,22 +1822,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122381949</v>
+        <v>122382824</v>
       </c>
       <c r="B12" t="n">
-        <v>79737</v>
+        <v>78656</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1841,21 +1850,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1865,10 +1874,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>563164</v>
+        <v>563010</v>
       </c>
       <c r="R12" t="n">
-        <v>7040871</v>
+        <v>7041054</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1900,7 +1909,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1910,7 +1919,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1925,22 +1934,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122381532</v>
+        <v>122383212</v>
       </c>
       <c r="B13" t="n">
-        <v>78656</v>
+        <v>90851</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1953,21 +1962,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1977,10 +1986,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>563324</v>
+        <v>562931</v>
       </c>
       <c r="R13" t="n">
-        <v>7040908</v>
+        <v>7041192</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2012,7 +2021,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2022,7 +2031,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2049,10 +2058,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122382457</v>
+        <v>122383327</v>
       </c>
       <c r="B14" t="n">
-        <v>90839</v>
+        <v>90851</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2065,21 +2074,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2089,10 +2098,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>563028</v>
+        <v>562914</v>
       </c>
       <c r="R14" t="n">
-        <v>7040950</v>
+        <v>7041282</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2124,7 +2133,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2134,7 +2143,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2161,10 +2170,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122384637</v>
+        <v>122381980</v>
       </c>
       <c r="B15" t="n">
-        <v>90857</v>
+        <v>78656</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2177,21 +2186,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2201,10 +2210,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>563210</v>
+        <v>563161</v>
       </c>
       <c r="R15" t="n">
-        <v>7040790</v>
+        <v>7040863</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2236,7 +2245,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2246,7 +2255,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2273,10 +2282,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122383248</v>
+        <v>122381949</v>
       </c>
       <c r="B16" t="n">
-        <v>90857</v>
+        <v>79737</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2289,21 +2298,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2313,10 +2322,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>562917</v>
+        <v>563164</v>
       </c>
       <c r="R16" t="n">
-        <v>7041224</v>
+        <v>7040871</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2348,7 +2357,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2358,7 +2367,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2385,10 +2394,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122381980</v>
+        <v>122383513</v>
       </c>
       <c r="B17" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2401,34 +2410,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>563161</v>
+        <v>562901</v>
       </c>
       <c r="R17" t="n">
-        <v>7040863</v>
+        <v>7041298</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2460,7 +2474,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2470,7 +2484,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2497,10 +2516,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122383513</v>
+        <v>122384843</v>
       </c>
       <c r="B18" t="n">
-        <v>57383</v>
+        <v>57399</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2513,16 +2532,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2533,7 +2552,7 @@
       <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2542,10 +2561,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>562901</v>
+        <v>563208</v>
       </c>
       <c r="R18" t="n">
-        <v>7041298</v>
+        <v>7040782</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2577,7 +2596,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2587,12 +2606,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:18</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2619,10 +2633,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122381544</v>
+        <v>122382457</v>
       </c>
       <c r="B19" t="n">
-        <v>78656</v>
+        <v>90833</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2635,21 +2649,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2659,10 +2673,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>563309</v>
+        <v>563028</v>
       </c>
       <c r="R19" t="n">
-        <v>7040893</v>
+        <v>7040950</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2694,7 +2708,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2704,7 +2718,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2731,10 +2745,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122384433</v>
+        <v>122381532</v>
       </c>
       <c r="B20" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2747,39 +2761,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>563163</v>
+        <v>563324</v>
       </c>
       <c r="R20" t="n">
-        <v>7040839</v>
+        <v>7040908</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2811,7 +2820,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2821,12 +2830,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:52</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2841,22 +2845,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122381566</v>
+        <v>122382572</v>
       </c>
       <c r="B21" t="n">
-        <v>82443</v>
+        <v>98240</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2865,38 +2869,42 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>563319</v>
+        <v>563035</v>
       </c>
       <c r="R21" t="n">
-        <v>7040899</v>
+        <v>7040943</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2928,7 +2936,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2938,7 +2946,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2965,10 +2973,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122382572</v>
+        <v>122383691</v>
       </c>
       <c r="B22" t="n">
-        <v>98237</v>
+        <v>57399</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2977,30 +2985,31 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3009,10 +3018,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>563035</v>
+        <v>562911</v>
       </c>
       <c r="R22" t="n">
-        <v>7040943</v>
+        <v>7041237</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3044,7 +3053,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3054,7 +3063,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3081,10 +3090,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122384291</v>
+        <v>122384637</v>
       </c>
       <c r="B23" t="n">
-        <v>90857</v>
+        <v>90851</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3114,26 +3123,17 @@
           <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>563130</v>
+        <v>563210</v>
       </c>
       <c r="R23" t="n">
-        <v>7040874</v>
+        <v>7040790</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3165,7 +3165,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3190,12 +3190,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>

--- a/artfynd/A 57317-2024 artfynd.xlsx
+++ b/artfynd/A 57317-2024 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122381544</v>
+        <v>122381949</v>
       </c>
       <c r="B3" t="n">
-        <v>78656</v>
+        <v>79737</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563309</v>
+        <v>563164</v>
       </c>
       <c r="R3" t="n">
-        <v>7040893</v>
+        <v>7040871</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122382979</v>
+        <v>122382726</v>
       </c>
       <c r="B4" t="n">
-        <v>57383</v>
+        <v>90851</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,39 +915,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562944</v>
+        <v>563044</v>
       </c>
       <c r="R4" t="n">
-        <v>7041093</v>
+        <v>7040945</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,12 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:45</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,7 +1011,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122384433</v>
+        <v>122384829</v>
       </c>
       <c r="B5" t="n">
         <v>57383</v>
@@ -1066,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563163</v>
+        <v>563205</v>
       </c>
       <c r="R5" t="n">
-        <v>7040839</v>
+        <v>7040789</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,12 +1101,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,22 +1121,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122381566</v>
+        <v>122384637</v>
       </c>
       <c r="B6" t="n">
-        <v>82443</v>
+        <v>90851</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1159,21 +1149,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1183,10 +1173,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563319</v>
+        <v>563210</v>
       </c>
       <c r="R6" t="n">
-        <v>7040899</v>
+        <v>7040790</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1218,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1228,7 +1218,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122381802</v>
+        <v>122381980</v>
       </c>
       <c r="B7" t="n">
-        <v>90851</v>
+        <v>78656</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1271,21 +1261,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1295,10 +1285,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>563191</v>
+        <v>563161</v>
       </c>
       <c r="R7" t="n">
-        <v>7040857</v>
+        <v>7040863</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1330,7 +1320,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1340,7 +1330,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1367,10 +1357,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122382726</v>
+        <v>122383513</v>
       </c>
       <c r="B8" t="n">
-        <v>90851</v>
+        <v>57383</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1383,34 +1373,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>563044</v>
+        <v>562901</v>
       </c>
       <c r="R8" t="n">
-        <v>7040945</v>
+        <v>7041298</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1442,7 +1437,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1452,7 +1447,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1479,10 +1479,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122382243</v>
+        <v>122383691</v>
       </c>
       <c r="B9" t="n">
-        <v>78656</v>
+        <v>57399</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1495,34 +1495,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>563125</v>
+        <v>562911</v>
       </c>
       <c r="R9" t="n">
-        <v>7040906</v>
+        <v>7041237</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1554,7 +1559,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1564,7 +1569,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1591,10 +1596,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122384829</v>
+        <v>122381566</v>
       </c>
       <c r="B10" t="n">
-        <v>57383</v>
+        <v>82443</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1607,39 +1612,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>563205</v>
+        <v>563319</v>
       </c>
       <c r="R10" t="n">
-        <v>7040789</v>
+        <v>7040899</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1681,12 +1681,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:16</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1713,10 +1708,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122384291</v>
+        <v>122384843</v>
       </c>
       <c r="B11" t="n">
-        <v>90851</v>
+        <v>57399</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1729,31 +1724,27 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1762,10 +1753,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>563130</v>
+        <v>563208</v>
       </c>
       <c r="R11" t="n">
-        <v>7040874</v>
+        <v>7040782</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1797,7 +1788,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1807,7 +1798,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1822,22 +1813,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122382824</v>
+        <v>122381802</v>
       </c>
       <c r="B12" t="n">
-        <v>78656</v>
+        <v>90851</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1850,21 +1841,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1874,10 +1865,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>563010</v>
+        <v>563191</v>
       </c>
       <c r="R12" t="n">
-        <v>7041054</v>
+        <v>7040857</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1909,7 +1900,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1919,7 +1910,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1934,12 +1925,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2058,10 +2049,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122383327</v>
+        <v>122382243</v>
       </c>
       <c r="B14" t="n">
-        <v>90851</v>
+        <v>78656</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2074,21 +2065,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2098,10 +2089,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>562914</v>
+        <v>563125</v>
       </c>
       <c r="R14" t="n">
-        <v>7041282</v>
+        <v>7040906</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2133,7 +2124,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2143,7 +2134,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2170,10 +2161,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122381980</v>
+        <v>122382572</v>
       </c>
       <c r="B15" t="n">
-        <v>78656</v>
+        <v>98240</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2182,38 +2173,42 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>563161</v>
+        <v>563035</v>
       </c>
       <c r="R15" t="n">
-        <v>7040863</v>
+        <v>7040943</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2245,7 +2240,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2255,7 +2250,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2282,10 +2277,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122381949</v>
+        <v>122383327</v>
       </c>
       <c r="B16" t="n">
-        <v>79737</v>
+        <v>90851</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2298,21 +2293,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2322,10 +2317,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>563164</v>
+        <v>562914</v>
       </c>
       <c r="R16" t="n">
-        <v>7040871</v>
+        <v>7041282</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2357,7 +2352,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2367,7 +2362,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2394,10 +2389,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122383513</v>
+        <v>122384291</v>
       </c>
       <c r="B17" t="n">
-        <v>57383</v>
+        <v>90851</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2410,27 +2405,31 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2439,10 +2438,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>562901</v>
+        <v>563130</v>
       </c>
       <c r="R17" t="n">
-        <v>7041298</v>
+        <v>7040874</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2474,7 +2473,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2484,12 +2483,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:18</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2504,22 +2498,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122384843</v>
+        <v>122382457</v>
       </c>
       <c r="B18" t="n">
-        <v>57399</v>
+        <v>90833</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2532,39 +2526,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>563208</v>
+        <v>563028</v>
       </c>
       <c r="R18" t="n">
-        <v>7040782</v>
+        <v>7040950</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2596,7 +2585,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2606,7 +2595,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2633,10 +2622,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122382457</v>
+        <v>122382979</v>
       </c>
       <c r="B19" t="n">
-        <v>90833</v>
+        <v>57383</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2649,34 +2638,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>563028</v>
+        <v>562944</v>
       </c>
       <c r="R19" t="n">
-        <v>7040950</v>
+        <v>7041093</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2708,7 +2702,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2718,7 +2712,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2745,10 +2744,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122381532</v>
+        <v>122384433</v>
       </c>
       <c r="B20" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2761,34 +2760,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>563324</v>
+        <v>563163</v>
       </c>
       <c r="R20" t="n">
-        <v>7040908</v>
+        <v>7040839</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2820,7 +2824,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2830,7 +2834,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2845,22 +2854,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122382572</v>
+        <v>122381544</v>
       </c>
       <c r="B21" t="n">
-        <v>98240</v>
+        <v>78656</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2869,42 +2878,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>563035</v>
+        <v>563309</v>
       </c>
       <c r="R21" t="n">
-        <v>7040943</v>
+        <v>7040893</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2936,7 +2941,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2946,7 +2951,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2973,10 +2978,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122383691</v>
+        <v>122382824</v>
       </c>
       <c r="B22" t="n">
-        <v>57399</v>
+        <v>78656</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2989,39 +2994,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>562911</v>
+        <v>563010</v>
       </c>
       <c r="R22" t="n">
-        <v>7041237</v>
+        <v>7041054</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3053,7 +3053,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3063,7 +3063,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3078,22 +3078,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122384637</v>
+        <v>122381532</v>
       </c>
       <c r="B23" t="n">
-        <v>90851</v>
+        <v>78656</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3106,21 +3106,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3130,10 +3130,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>563210</v>
+        <v>563324</v>
       </c>
       <c r="R23" t="n">
-        <v>7040790</v>
+        <v>7040908</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3165,7 +3165,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 57317-2024 artfynd.xlsx
+++ b/artfynd/A 57317-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122383248</v>
+        <v>122384829</v>
       </c>
       <c r="B2" t="n">
-        <v>90851</v>
+        <v>57384</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>562917</v>
+        <v>563205</v>
       </c>
       <c r="R2" t="n">
-        <v>7041224</v>
+        <v>7040789</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122381949</v>
+        <v>122381802</v>
       </c>
       <c r="B3" t="n">
-        <v>79737</v>
+        <v>90852</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +813,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563164</v>
+        <v>563191</v>
       </c>
       <c r="R3" t="n">
-        <v>7040871</v>
+        <v>7040857</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122382726</v>
+        <v>122382572</v>
       </c>
       <c r="B4" t="n">
-        <v>90851</v>
+        <v>98241</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,38 +921,42 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563044</v>
+        <v>563035</v>
       </c>
       <c r="R4" t="n">
-        <v>7040945</v>
+        <v>7040943</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +988,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +998,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1025,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122384829</v>
+        <v>122383691</v>
       </c>
       <c r="B5" t="n">
-        <v>57383</v>
+        <v>57400</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,16 +1041,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1056,10 +1070,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563205</v>
+        <v>562911</v>
       </c>
       <c r="R5" t="n">
-        <v>7040789</v>
+        <v>7041237</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,7 +1105,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,12 +1115,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:16</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,10 +1142,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122384637</v>
+        <v>122381980</v>
       </c>
       <c r="B6" t="n">
-        <v>90851</v>
+        <v>78657</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,21 +1158,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1173,10 +1182,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563210</v>
+        <v>563161</v>
       </c>
       <c r="R6" t="n">
-        <v>7040790</v>
+        <v>7040863</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1208,7 +1217,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,7 +1227,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,10 +1254,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122381980</v>
+        <v>122383513</v>
       </c>
       <c r="B7" t="n">
-        <v>78656</v>
+        <v>57384</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1261,34 +1270,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>563161</v>
+        <v>562901</v>
       </c>
       <c r="R7" t="n">
-        <v>7040863</v>
+        <v>7041298</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1320,7 +1334,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1330,7 +1344,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1357,10 +1376,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122383513</v>
+        <v>122383248</v>
       </c>
       <c r="B8" t="n">
-        <v>57383</v>
+        <v>90852</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1373,39 +1392,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>562901</v>
+        <v>562917</v>
       </c>
       <c r="R8" t="n">
-        <v>7041298</v>
+        <v>7041224</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1437,7 +1451,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1447,12 +1461,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:18</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1479,10 +1488,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122383691</v>
+        <v>122381544</v>
       </c>
       <c r="B9" t="n">
-        <v>57399</v>
+        <v>78657</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1495,39 +1504,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>562911</v>
+        <v>563309</v>
       </c>
       <c r="R9" t="n">
-        <v>7041237</v>
+        <v>7040893</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1559,7 +1563,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1569,7 +1573,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1596,10 +1600,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122381566</v>
+        <v>122382243</v>
       </c>
       <c r="B10" t="n">
-        <v>82443</v>
+        <v>78657</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1612,21 +1616,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1636,10 +1640,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>563319</v>
+        <v>563125</v>
       </c>
       <c r="R10" t="n">
-        <v>7040899</v>
+        <v>7040906</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1671,7 +1675,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1681,7 +1685,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1708,10 +1712,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122384843</v>
+        <v>122384433</v>
       </c>
       <c r="B11" t="n">
-        <v>57399</v>
+        <v>57384</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1724,16 +1728,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1753,10 +1757,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>563208</v>
+        <v>563163</v>
       </c>
       <c r="R11" t="n">
-        <v>7040782</v>
+        <v>7040839</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1788,7 +1792,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1798,7 +1802,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1813,22 +1822,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122381802</v>
+        <v>122382457</v>
       </c>
       <c r="B12" t="n">
-        <v>90851</v>
+        <v>90834</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1841,21 +1850,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1865,10 +1874,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>563191</v>
+        <v>563028</v>
       </c>
       <c r="R12" t="n">
-        <v>7040857</v>
+        <v>7040950</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1900,7 +1909,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1910,7 +1919,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1937,10 +1946,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122383212</v>
+        <v>122382979</v>
       </c>
       <c r="B13" t="n">
-        <v>90851</v>
+        <v>57384</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1953,34 +1962,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>562931</v>
+        <v>562944</v>
       </c>
       <c r="R13" t="n">
-        <v>7041192</v>
+        <v>7041093</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2012,7 +2026,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2022,7 +2036,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2049,10 +2068,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122382243</v>
+        <v>122384637</v>
       </c>
       <c r="B14" t="n">
-        <v>78656</v>
+        <v>90852</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2065,21 +2084,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2089,10 +2108,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>563125</v>
+        <v>563210</v>
       </c>
       <c r="R14" t="n">
-        <v>7040906</v>
+        <v>7040790</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2124,7 +2143,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2134,7 +2153,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2161,10 +2180,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122382572</v>
+        <v>122384291</v>
       </c>
       <c r="B15" t="n">
-        <v>98240</v>
+        <v>90852</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2173,25 +2192,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2199,16 +2218,21 @@
           <t>3</t>
         </is>
       </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>563035</v>
+        <v>563130</v>
       </c>
       <c r="R15" t="n">
-        <v>7040943</v>
+        <v>7040874</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2240,7 +2264,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2250,7 +2274,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2265,22 +2289,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122383327</v>
+        <v>122381566</v>
       </c>
       <c r="B16" t="n">
-        <v>90851</v>
+        <v>82444</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2293,21 +2317,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2317,10 +2341,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>562914</v>
+        <v>563319</v>
       </c>
       <c r="R16" t="n">
-        <v>7041282</v>
+        <v>7040899</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2352,7 +2376,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2362,7 +2386,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2389,10 +2413,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122384291</v>
+        <v>122381532</v>
       </c>
       <c r="B17" t="n">
-        <v>90851</v>
+        <v>78657</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2405,43 +2429,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>563130</v>
+        <v>563324</v>
       </c>
       <c r="R17" t="n">
-        <v>7040874</v>
+        <v>7040908</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2473,7 +2488,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2483,7 +2498,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2498,22 +2513,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122382457</v>
+        <v>122383212</v>
       </c>
       <c r="B18" t="n">
-        <v>90833</v>
+        <v>90852</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2526,21 +2541,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2550,10 +2565,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>563028</v>
+        <v>562931</v>
       </c>
       <c r="R18" t="n">
-        <v>7040950</v>
+        <v>7041192</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2585,7 +2600,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2595,7 +2610,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2622,10 +2637,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122382979</v>
+        <v>122381949</v>
       </c>
       <c r="B19" t="n">
-        <v>57383</v>
+        <v>79738</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2638,39 +2653,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>562944</v>
+        <v>563164</v>
       </c>
       <c r="R19" t="n">
-        <v>7041093</v>
+        <v>7040871</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2702,7 +2712,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2712,12 +2722,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:45</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2744,10 +2749,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122384433</v>
+        <v>122384843</v>
       </c>
       <c r="B20" t="n">
-        <v>57383</v>
+        <v>57400</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2760,16 +2765,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2789,10 +2794,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>563163</v>
+        <v>563208</v>
       </c>
       <c r="R20" t="n">
-        <v>7040839</v>
+        <v>7040782</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2824,7 +2829,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2834,12 +2839,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:52</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2854,22 +2854,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122381544</v>
+        <v>122382824</v>
       </c>
       <c r="B21" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2906,10 +2906,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>563309</v>
+        <v>563010</v>
       </c>
       <c r="R21" t="n">
-        <v>7040893</v>
+        <v>7041054</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2941,7 +2941,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2966,22 +2966,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122382824</v>
+        <v>122382726</v>
       </c>
       <c r="B22" t="n">
-        <v>78656</v>
+        <v>90852</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2994,21 +2994,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3018,10 +3018,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>563010</v>
+        <v>563044</v>
       </c>
       <c r="R22" t="n">
-        <v>7041054</v>
+        <v>7040945</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3053,7 +3053,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3063,7 +3063,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3078,22 +3078,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122381532</v>
+        <v>122383327</v>
       </c>
       <c r="B23" t="n">
-        <v>78656</v>
+        <v>90852</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3106,21 +3106,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3130,10 +3130,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>563324</v>
+        <v>562914</v>
       </c>
       <c r="R23" t="n">
-        <v>7040908</v>
+        <v>7041282</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3165,7 +3165,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 57317-2024 artfynd.xlsx
+++ b/artfynd/A 57317-2024 artfynd.xlsx
@@ -2068,10 +2068,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122384637</v>
+        <v>122381566</v>
       </c>
       <c r="B14" t="n">
-        <v>90852</v>
+        <v>82444</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2084,21 +2084,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2108,10 +2108,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>563210</v>
+        <v>563319</v>
       </c>
       <c r="R14" t="n">
-        <v>7040790</v>
+        <v>7040899</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2143,7 +2143,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2153,7 +2153,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2180,7 +2180,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122384291</v>
+        <v>122384637</v>
       </c>
       <c r="B15" t="n">
         <v>90852</v>
@@ -2213,26 +2213,17 @@
           <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>563130</v>
+        <v>563210</v>
       </c>
       <c r="R15" t="n">
-        <v>7040874</v>
+        <v>7040790</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2264,7 +2255,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2274,7 +2265,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2289,22 +2280,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122381566</v>
+        <v>122384291</v>
       </c>
       <c r="B16" t="n">
-        <v>82444</v>
+        <v>90852</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2317,34 +2308,43 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>563319</v>
+        <v>563130</v>
       </c>
       <c r="R16" t="n">
-        <v>7040899</v>
+        <v>7040874</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2401,12 +2401,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>

--- a/artfynd/A 57317-2024 artfynd.xlsx
+++ b/artfynd/A 57317-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122384829</v>
+        <v>122382243</v>
       </c>
       <c r="B2" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>563205</v>
+        <v>563125</v>
       </c>
       <c r="R2" t="n">
-        <v>7040789</v>
+        <v>7040906</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:16</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122381802</v>
+        <v>122381532</v>
       </c>
       <c r="B3" t="n">
-        <v>90852</v>
+        <v>78660</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -837,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563191</v>
+        <v>563324</v>
       </c>
       <c r="R3" t="n">
-        <v>7040857</v>
+        <v>7040908</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122382572</v>
+        <v>122381949</v>
       </c>
       <c r="B4" t="n">
-        <v>98241</v>
+        <v>79741</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,42 +911,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563035</v>
+        <v>563164</v>
       </c>
       <c r="R4" t="n">
-        <v>7040943</v>
+        <v>7040871</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -988,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -998,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122383691</v>
+        <v>122381544</v>
       </c>
       <c r="B5" t="n">
-        <v>57400</v>
+        <v>78660</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1041,39 +1027,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562911</v>
+        <v>563309</v>
       </c>
       <c r="R5" t="n">
-        <v>7041237</v>
+        <v>7040893</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1105,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1115,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1142,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122381980</v>
+        <v>122384843</v>
       </c>
       <c r="B6" t="n">
-        <v>78657</v>
+        <v>57400</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1158,34 +1139,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563161</v>
+        <v>563208</v>
       </c>
       <c r="R6" t="n">
-        <v>7040863</v>
+        <v>7040782</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1217,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1227,7 +1213,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1254,10 +1240,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122383513</v>
+        <v>122383248</v>
       </c>
       <c r="B7" t="n">
-        <v>57384</v>
+        <v>90855</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1270,39 +1256,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>562901</v>
+        <v>562917</v>
       </c>
       <c r="R7" t="n">
-        <v>7041298</v>
+        <v>7041224</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1334,7 +1315,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1344,12 +1325,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:18</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1376,10 +1352,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122383248</v>
+        <v>122382726</v>
       </c>
       <c r="B8" t="n">
-        <v>90852</v>
+        <v>90855</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1416,10 +1392,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>562917</v>
+        <v>563044</v>
       </c>
       <c r="R8" t="n">
-        <v>7041224</v>
+        <v>7040945</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1451,7 +1427,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1461,7 +1437,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1488,10 +1464,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122381544</v>
+        <v>122384433</v>
       </c>
       <c r="B9" t="n">
-        <v>78657</v>
+        <v>57384</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1504,34 +1480,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>563309</v>
+        <v>563163</v>
       </c>
       <c r="R9" t="n">
-        <v>7040893</v>
+        <v>7040839</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1563,7 +1544,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1573,7 +1554,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1588,22 +1574,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122382243</v>
+        <v>122382979</v>
       </c>
       <c r="B10" t="n">
-        <v>78657</v>
+        <v>57384</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1616,34 +1602,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>563125</v>
+        <v>562944</v>
       </c>
       <c r="R10" t="n">
-        <v>7040906</v>
+        <v>7041093</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1675,7 +1666,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1685,7 +1676,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1712,7 +1708,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122384433</v>
+        <v>122384829</v>
       </c>
       <c r="B11" t="n">
         <v>57384</v>
@@ -1757,10 +1753,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>563163</v>
+        <v>563205</v>
       </c>
       <c r="R11" t="n">
-        <v>7040839</v>
+        <v>7040789</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1792,7 +1788,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1802,12 +1798,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1822,22 +1818,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122382457</v>
+        <v>122381980</v>
       </c>
       <c r="B12" t="n">
-        <v>90834</v>
+        <v>78660</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1850,21 +1846,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1874,10 +1870,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>563028</v>
+        <v>563161</v>
       </c>
       <c r="R12" t="n">
-        <v>7040950</v>
+        <v>7040863</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1909,7 +1905,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1919,7 +1915,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1946,10 +1942,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122382979</v>
+        <v>122383691</v>
       </c>
       <c r="B13" t="n">
-        <v>57384</v>
+        <v>57400</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1962,16 +1958,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1982,7 +1978,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1991,10 +1987,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>562944</v>
+        <v>562911</v>
       </c>
       <c r="R13" t="n">
-        <v>7041093</v>
+        <v>7041237</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2026,7 +2022,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2036,12 +2032,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:45</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2068,10 +2059,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122381566</v>
+        <v>122382572</v>
       </c>
       <c r="B14" t="n">
-        <v>82444</v>
+        <v>98244</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2080,38 +2071,42 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>563319</v>
+        <v>563035</v>
       </c>
       <c r="R14" t="n">
-        <v>7040899</v>
+        <v>7040943</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2143,7 +2138,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2153,7 +2148,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2183,7 +2178,7 @@
         <v>122384637</v>
       </c>
       <c r="B15" t="n">
-        <v>90852</v>
+        <v>90855</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2295,7 +2290,7 @@
         <v>122384291</v>
       </c>
       <c r="B16" t="n">
-        <v>90852</v>
+        <v>90855</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2413,10 +2408,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122381532</v>
+        <v>122382824</v>
       </c>
       <c r="B17" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2453,10 +2448,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>563324</v>
+        <v>563010</v>
       </c>
       <c r="R17" t="n">
-        <v>7040908</v>
+        <v>7041054</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2488,7 +2483,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2498,7 +2493,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2513,22 +2508,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122383212</v>
+        <v>122382457</v>
       </c>
       <c r="B18" t="n">
-        <v>90852</v>
+        <v>90837</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2541,21 +2536,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2565,10 +2560,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>562931</v>
+        <v>563028</v>
       </c>
       <c r="R18" t="n">
-        <v>7041192</v>
+        <v>7040950</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2600,7 +2595,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2610,7 +2605,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2637,10 +2632,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122381949</v>
+        <v>122381566</v>
       </c>
       <c r="B19" t="n">
-        <v>79738</v>
+        <v>82447</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2653,21 +2648,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2677,10 +2672,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>563164</v>
+        <v>563319</v>
       </c>
       <c r="R19" t="n">
-        <v>7040871</v>
+        <v>7040899</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2712,7 +2707,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2722,7 +2717,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2749,10 +2744,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122384843</v>
+        <v>122383513</v>
       </c>
       <c r="B20" t="n">
-        <v>57400</v>
+        <v>57384</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2765,16 +2760,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2785,7 +2780,7 @@
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2794,10 +2789,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>563208</v>
+        <v>562901</v>
       </c>
       <c r="R20" t="n">
-        <v>7040782</v>
+        <v>7041298</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2829,7 +2824,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2839,7 +2834,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2866,10 +2866,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122382824</v>
+        <v>122383212</v>
       </c>
       <c r="B21" t="n">
-        <v>78657</v>
+        <v>90855</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2882,21 +2882,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2906,10 +2906,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>563010</v>
+        <v>562931</v>
       </c>
       <c r="R21" t="n">
-        <v>7041054</v>
+        <v>7041192</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2941,7 +2941,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2966,22 +2966,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122382726</v>
+        <v>122381802</v>
       </c>
       <c r="B22" t="n">
-        <v>90852</v>
+        <v>90855</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3018,10 +3018,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>563044</v>
+        <v>563191</v>
       </c>
       <c r="R22" t="n">
-        <v>7040945</v>
+        <v>7040857</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3053,7 +3053,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3063,7 +3063,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3093,7 +3093,7 @@
         <v>122383327</v>
       </c>
       <c r="B23" t="n">
-        <v>90852</v>
+        <v>90855</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>

--- a/artfynd/A 57317-2024 artfynd.xlsx
+++ b/artfynd/A 57317-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122382243</v>
+        <v>122383691</v>
       </c>
       <c r="B2" t="n">
-        <v>78660</v>
+        <v>57400</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>563125</v>
+        <v>562911</v>
       </c>
       <c r="R2" t="n">
-        <v>7040906</v>
+        <v>7041237</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122381532</v>
+        <v>122381802</v>
       </c>
       <c r="B3" t="n">
-        <v>78660</v>
+        <v>90855</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +808,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563324</v>
+        <v>563191</v>
       </c>
       <c r="R3" t="n">
-        <v>7040908</v>
+        <v>7040857</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122381949</v>
+        <v>122383212</v>
       </c>
       <c r="B4" t="n">
-        <v>79741</v>
+        <v>90855</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +920,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563164</v>
+        <v>562931</v>
       </c>
       <c r="R4" t="n">
-        <v>7040871</v>
+        <v>7041192</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122381544</v>
+        <v>122381566</v>
       </c>
       <c r="B5" t="n">
-        <v>78660</v>
+        <v>82447</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,21 +1032,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563309</v>
+        <v>563319</v>
       </c>
       <c r="R5" t="n">
-        <v>7040893</v>
+        <v>7040899</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122384843</v>
+        <v>122383248</v>
       </c>
       <c r="B6" t="n">
-        <v>57400</v>
+        <v>90855</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,39 +1144,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563208</v>
+        <v>562917</v>
       </c>
       <c r="R6" t="n">
-        <v>7040782</v>
+        <v>7041224</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,7 +1240,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122383248</v>
+        <v>122382726</v>
       </c>
       <c r="B7" t="n">
         <v>90855</v>
@@ -1280,10 +1280,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>562917</v>
+        <v>563044</v>
       </c>
       <c r="R7" t="n">
-        <v>7041224</v>
+        <v>7040945</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1352,10 +1352,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122382726</v>
+        <v>122384433</v>
       </c>
       <c r="B8" t="n">
-        <v>90855</v>
+        <v>57384</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1368,34 +1368,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>563044</v>
+        <v>563163</v>
       </c>
       <c r="R8" t="n">
-        <v>7040945</v>
+        <v>7040839</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1427,7 +1432,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1437,7 +1442,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1452,22 +1462,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122384433</v>
+        <v>122382457</v>
       </c>
       <c r="B9" t="n">
-        <v>57384</v>
+        <v>90837</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1480,39 +1490,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>563163</v>
+        <v>563028</v>
       </c>
       <c r="R9" t="n">
-        <v>7040839</v>
+        <v>7040950</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1544,7 +1549,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1554,12 +1559,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:52</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1574,22 +1574,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122382979</v>
+        <v>122384637</v>
       </c>
       <c r="B10" t="n">
-        <v>57384</v>
+        <v>90855</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1602,39 +1602,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>562944</v>
+        <v>563210</v>
       </c>
       <c r="R10" t="n">
-        <v>7041093</v>
+        <v>7040790</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1666,7 +1661,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1676,12 +1671,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:45</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1708,7 +1698,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122384829</v>
+        <v>122383513</v>
       </c>
       <c r="B11" t="n">
         <v>57384</v>
@@ -1744,7 +1734,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1753,10 +1743,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>563205</v>
+        <v>562901</v>
       </c>
       <c r="R11" t="n">
-        <v>7040789</v>
+        <v>7041298</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1788,7 +1778,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1798,7 +1788,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1830,10 +1820,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122381980</v>
+        <v>122383327</v>
       </c>
       <c r="B12" t="n">
-        <v>78660</v>
+        <v>90855</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1846,21 +1836,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1870,10 +1860,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>563161</v>
+        <v>562914</v>
       </c>
       <c r="R12" t="n">
-        <v>7040863</v>
+        <v>7041282</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1905,7 +1895,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1915,7 +1905,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1942,10 +1932,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122383691</v>
+        <v>122381949</v>
       </c>
       <c r="B13" t="n">
-        <v>57400</v>
+        <v>79741</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1958,39 +1948,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>562911</v>
+        <v>563164</v>
       </c>
       <c r="R13" t="n">
-        <v>7041237</v>
+        <v>7040871</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2022,7 +2007,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2032,7 +2017,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2059,10 +2044,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122382572</v>
+        <v>122384829</v>
       </c>
       <c r="B14" t="n">
-        <v>98244</v>
+        <v>57384</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2071,30 +2056,31 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2103,10 +2089,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>563035</v>
+        <v>563205</v>
       </c>
       <c r="R14" t="n">
-        <v>7040943</v>
+        <v>7040789</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2138,7 +2124,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2148,7 +2134,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2175,10 +2166,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122384637</v>
+        <v>122381544</v>
       </c>
       <c r="B15" t="n">
-        <v>90855</v>
+        <v>78660</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2191,21 +2182,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2215,10 +2206,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>563210</v>
+        <v>563309</v>
       </c>
       <c r="R15" t="n">
-        <v>7040790</v>
+        <v>7040893</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2250,7 +2241,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2260,7 +2251,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2287,10 +2278,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122384291</v>
+        <v>122382824</v>
       </c>
       <c r="B16" t="n">
-        <v>90855</v>
+        <v>78660</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2303,43 +2294,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>563130</v>
+        <v>563010</v>
       </c>
       <c r="R16" t="n">
-        <v>7040874</v>
+        <v>7041054</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2371,7 +2353,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2381,7 +2363,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2408,7 +2390,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122382824</v>
+        <v>122381532</v>
       </c>
       <c r="B17" t="n">
         <v>78660</v>
@@ -2448,10 +2430,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>563010</v>
+        <v>563324</v>
       </c>
       <c r="R17" t="n">
-        <v>7041054</v>
+        <v>7040908</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2483,7 +2465,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2493,7 +2475,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2508,22 +2490,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122382457</v>
+        <v>122382572</v>
       </c>
       <c r="B18" t="n">
-        <v>90837</v>
+        <v>98244</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2532,38 +2514,42 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>563028</v>
+        <v>563035</v>
       </c>
       <c r="R18" t="n">
-        <v>7040950</v>
+        <v>7040943</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2595,7 +2581,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2605,7 +2591,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2632,10 +2618,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122381566</v>
+        <v>122384291</v>
       </c>
       <c r="B19" t="n">
-        <v>82447</v>
+        <v>90855</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2648,34 +2634,43 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>563319</v>
+        <v>563130</v>
       </c>
       <c r="R19" t="n">
-        <v>7040899</v>
+        <v>7040874</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2707,7 +2702,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2717,7 +2712,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2732,22 +2727,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122383513</v>
+        <v>122381980</v>
       </c>
       <c r="B20" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2760,39 +2755,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>562901</v>
+        <v>563161</v>
       </c>
       <c r="R20" t="n">
-        <v>7041298</v>
+        <v>7040863</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2824,7 +2814,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2834,12 +2824,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:18</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2866,10 +2851,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122383212</v>
+        <v>122382243</v>
       </c>
       <c r="B21" t="n">
-        <v>90855</v>
+        <v>78660</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2882,21 +2867,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2906,10 +2891,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>562931</v>
+        <v>563125</v>
       </c>
       <c r="R21" t="n">
-        <v>7041192</v>
+        <v>7040906</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2941,7 +2926,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2951,7 +2936,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2978,10 +2963,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122381802</v>
+        <v>122384843</v>
       </c>
       <c r="B22" t="n">
-        <v>90855</v>
+        <v>57400</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2994,34 +2979,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>563191</v>
+        <v>563208</v>
       </c>
       <c r="R22" t="n">
-        <v>7040857</v>
+        <v>7040782</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3053,7 +3043,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3063,7 +3053,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3090,10 +3080,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122383327</v>
+        <v>122382979</v>
       </c>
       <c r="B23" t="n">
-        <v>90855</v>
+        <v>57384</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3106,34 +3096,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>562914</v>
+        <v>562944</v>
       </c>
       <c r="R23" t="n">
-        <v>7041282</v>
+        <v>7041093</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3165,7 +3160,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3175,7 +3170,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 57317-2024 artfynd.xlsx
+++ b/artfynd/A 57317-2024 artfynd.xlsx
@@ -2963,10 +2963,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122384843</v>
+        <v>122382979</v>
       </c>
       <c r="B22" t="n">
-        <v>57400</v>
+        <v>57384</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2979,16 +2979,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2999,7 +2999,7 @@
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3008,10 +3008,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>563208</v>
+        <v>562944</v>
       </c>
       <c r="R22" t="n">
-        <v>7040782</v>
+        <v>7041093</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3043,7 +3043,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3053,7 +3053,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3080,10 +3085,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122382979</v>
+        <v>122384843</v>
       </c>
       <c r="B23" t="n">
-        <v>57384</v>
+        <v>57400</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3096,16 +3101,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3116,7 +3121,7 @@
       <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3125,10 +3130,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>562944</v>
+        <v>563208</v>
       </c>
       <c r="R23" t="n">
-        <v>7041093</v>
+        <v>7040782</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3160,7 +3165,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3170,12 +3175,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:45</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 57317-2024 artfynd.xlsx
+++ b/artfynd/A 57317-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122383691</v>
+        <v>122381646</v>
       </c>
       <c r="B2" t="n">
-        <v>57400</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>562911</v>
+        <v>563261</v>
       </c>
       <c r="R2" t="n">
-        <v>7041237</v>
+        <v>7040864</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,15 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122381802</v>
+        <v>122382457</v>
       </c>
       <c r="B3" t="n">
-        <v>90855</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563191</v>
+        <v>563028</v>
       </c>
       <c r="R3" t="n">
-        <v>7040857</v>
+        <v>7040950</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,15 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122383212</v>
+        <v>122381566</v>
       </c>
       <c r="B4" t="n">
-        <v>90855</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -920,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -944,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562931</v>
+        <v>563319</v>
       </c>
       <c r="R4" t="n">
-        <v>7041192</v>
+        <v>7040899</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,15 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122381566</v>
+        <v>122381792</v>
       </c>
       <c r="B5" t="n">
-        <v>82447</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1056,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563319</v>
+        <v>563215</v>
       </c>
       <c r="R5" t="n">
-        <v>7040899</v>
+        <v>7040872</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,37 +1103,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122383248</v>
+        <v>122381532</v>
       </c>
       <c r="B6" t="n">
-        <v>90855</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1168,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>562917</v>
+        <v>563324</v>
       </c>
       <c r="R6" t="n">
-        <v>7041224</v>
+        <v>7040908</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1203,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,37 +1210,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122382726</v>
+        <v>122381544</v>
       </c>
       <c r="B7" t="n">
-        <v>90855</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1280,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>563044</v>
+        <v>563309</v>
       </c>
       <c r="R7" t="n">
-        <v>7040945</v>
+        <v>7040893</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1315,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1325,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1352,55 +1317,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122384433</v>
+        <v>122381980</v>
       </c>
       <c r="B8" t="n">
-        <v>57384</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>563163</v>
+        <v>563161</v>
       </c>
       <c r="R8" t="n">
-        <v>7040839</v>
+        <v>7040863</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1432,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1442,12 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:52</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1462,49 +1412,44 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122382457</v>
+        <v>122382243</v>
       </c>
       <c r="B9" t="n">
-        <v>90837</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1514,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>563028</v>
+        <v>563125</v>
       </c>
       <c r="R9" t="n">
-        <v>7040950</v>
+        <v>7040906</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1549,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1559,7 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1586,55 +1531,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122383513</v>
+        <v>122382824</v>
       </c>
       <c r="B10" t="n">
-        <v>57384</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>562901</v>
+        <v>563010</v>
       </c>
       <c r="R10" t="n">
-        <v>7041298</v>
+        <v>7041054</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1666,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1676,12 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:18</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1696,27 +1626,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122384637</v>
+        <v>122381949</v>
       </c>
       <c r="B11" t="n">
-        <v>90855</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1724,21 +1649,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1748,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>563210</v>
+        <v>563164</v>
       </c>
       <c r="R11" t="n">
-        <v>7040790</v>
+        <v>7040871</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1783,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1793,7 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1820,50 +1745,50 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122383327</v>
+        <v>122383691</v>
       </c>
       <c r="B12" t="n">
-        <v>90855</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>562914</v>
+        <v>562911</v>
       </c>
       <c r="R12" t="n">
-        <v>7041282</v>
+        <v>7041237</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1895,7 +1820,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1905,7 +1830,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1932,50 +1857,50 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122381949</v>
+        <v>122384843</v>
       </c>
       <c r="B13" t="n">
-        <v>79741</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>563164</v>
+        <v>563208</v>
       </c>
       <c r="R13" t="n">
-        <v>7040871</v>
+        <v>7040782</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2007,7 +1932,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2017,7 +1942,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2044,15 +1969,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122384829</v>
+        <v>122382979</v>
       </c>
       <c r="B14" t="n">
-        <v>57384</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2080,7 +2000,7 @@
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2089,10 +2009,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>563205</v>
+        <v>562944</v>
       </c>
       <c r="R14" t="n">
-        <v>7040789</v>
+        <v>7041093</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2124,7 +2044,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2134,7 +2054,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2166,15 +2086,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122381544</v>
+        <v>122383513</v>
       </c>
       <c r="B15" t="n">
-        <v>78660</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2182,34 +2097,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>563309</v>
+        <v>562901</v>
       </c>
       <c r="R15" t="n">
-        <v>7040893</v>
+        <v>7041298</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2241,7 +2161,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2251,7 +2171,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2278,15 +2203,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122382824</v>
+        <v>122384433</v>
       </c>
       <c r="B16" t="n">
-        <v>78660</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2294,34 +2214,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>563010</v>
+        <v>563163</v>
       </c>
       <c r="R16" t="n">
-        <v>7041054</v>
+        <v>7040839</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2353,7 +2278,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2363,7 +2288,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2390,15 +2320,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122381532</v>
+        <v>122384829</v>
       </c>
       <c r="B17" t="n">
-        <v>78660</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2406,34 +2331,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>563324</v>
+        <v>563205</v>
       </c>
       <c r="R17" t="n">
-        <v>7040908</v>
+        <v>7040789</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2465,7 +2395,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2475,7 +2405,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2505,12 +2440,7 @@
         <v>122382572</v>
       </c>
       <c r="B18" t="n">
-        <v>98244</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2615,590 +2545,6 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>122384291</v>
-      </c>
-      <c r="B19" t="n">
-        <v>90855</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>Flarmyran, Flarmyran, Ång</t>
-        </is>
-      </c>
-      <c r="Q19" t="n">
-        <v>563130</v>
-      </c>
-      <c r="R19" t="n">
-        <v>7040874</v>
-      </c>
-      <c r="S19" t="n">
-        <v>10</v>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>Ramsele</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>2025-01-30</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>14:45</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>2025-01-30</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>14:45</t>
-        </is>
-      </c>
-      <c r="AD19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT19" t="inlineStr"/>
-      <c r="AW19" t="inlineStr">
-        <is>
-          <t>Kamilla Andersson</t>
-        </is>
-      </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>Kamilla Andersson</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>122382979</v>
-      </c>
-      <c r="B20" t="n">
-        <v>57384</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>Flarmyran, Flarmyran, Ång</t>
-        </is>
-      </c>
-      <c r="Q20" t="n">
-        <v>562944</v>
-      </c>
-      <c r="R20" t="n">
-        <v>7041093</v>
-      </c>
-      <c r="S20" t="n">
-        <v>10</v>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>Ramsele</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>2025-01-30</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>13:45</t>
-        </is>
-      </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>2025-01-30</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>13:45</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
-      <c r="AD20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT20" t="inlineStr"/>
-      <c r="AW20" t="inlineStr">
-        <is>
-          <t>Kim Hultgren</t>
-        </is>
-      </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>Kim Hultgren</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>122381980</v>
-      </c>
-      <c r="B21" t="n">
-        <v>78660</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>Flarmyran, Flarmyran, Ång</t>
-        </is>
-      </c>
-      <c r="Q21" t="n">
-        <v>563161</v>
-      </c>
-      <c r="R21" t="n">
-        <v>7040863</v>
-      </c>
-      <c r="S21" t="n">
-        <v>10</v>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>Ramsele</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>2025-01-30</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>12:34</t>
-        </is>
-      </c>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>2025-01-30</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>12:34</t>
-        </is>
-      </c>
-      <c r="AD21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT21" t="inlineStr"/>
-      <c r="AW21" t="inlineStr">
-        <is>
-          <t>Kim Hultgren</t>
-        </is>
-      </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>Kim Hultgren</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>122382243</v>
-      </c>
-      <c r="B22" t="n">
-        <v>78660</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>Flarmyran, Flarmyran, Ång</t>
-        </is>
-      </c>
-      <c r="Q22" t="n">
-        <v>563125</v>
-      </c>
-      <c r="R22" t="n">
-        <v>7040906</v>
-      </c>
-      <c r="S22" t="n">
-        <v>10</v>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>Ramsele</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>2025-01-30</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>12:52</t>
-        </is>
-      </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>2025-01-30</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>12:52</t>
-        </is>
-      </c>
-      <c r="AD22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT22" t="inlineStr"/>
-      <c r="AW22" t="inlineStr">
-        <is>
-          <t>Kim Hultgren</t>
-        </is>
-      </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>Kim Hultgren</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>122384843</v>
-      </c>
-      <c r="B23" t="n">
-        <v>57400</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>Flarmyran, Flarmyran, Ång</t>
-        </is>
-      </c>
-      <c r="Q23" t="n">
-        <v>563208</v>
-      </c>
-      <c r="R23" t="n">
-        <v>7040782</v>
-      </c>
-      <c r="S23" t="n">
-        <v>10</v>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>Ramsele</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>2025-01-30</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>15:18</t>
-        </is>
-      </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>2025-01-30</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>15:18</t>
-        </is>
-      </c>
-      <c r="AD23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT23" t="inlineStr"/>
-      <c r="AW23" t="inlineStr">
-        <is>
-          <t>Kim Hultgren</t>
-        </is>
-      </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>Kim Hultgren</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 57317-2024 artfynd.xlsx
+++ b/artfynd/A 57317-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122381646</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122382457</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122381566</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122381792</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122381532</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122381544</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1421,6 +1456,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122381980</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1528,6 +1568,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122382243</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1635,6 +1680,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122382824</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1742,6 +1792,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122381949</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1854,6 +1909,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122383691</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1966,6 +2026,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122384843</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2083,6 +2148,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122382979</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2200,6 +2270,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122383513</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2317,6 +2392,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122384433</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2434,6 +2514,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122384829</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2545,8 +2630,32 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122382572</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>